--- a/final.xlsx
+++ b/final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\MEGA\3. BAGI HASIL\8. Agustus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45D1CEDE-A95B-4D70-94F7-D137E5BD2865}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A2C9B53-2015-4F3B-9744-6E1757443D9B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
     <definedName name="_6462Tarif_2_1">"$#REF!.$C$48:$D$55"</definedName>
     <definedName name="_65a_3_2">"$#REF!.$A$3:$E$425"</definedName>
     <definedName name="_7003TRF_2_1">"'file://Talafspu401/ccr/Data Induk Prod.Dept/Bonus produksi/3.Incentive KPP/06.Desember.xls'#$'Master '.$#REF!$#REF!:$#REF!$#REF!"</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">RAW!$A$4:$AH$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">RAW!$A$4:$AG$13</definedName>
     <definedName name="a_1">"$#REF!.$A$3:$E$425"</definedName>
     <definedName name="a_1_1">"$#REF!.$A$3:$E$425"</definedName>
     <definedName name="a_2">"$#REF!.$A$3:$E$425"</definedName>
@@ -284,7 +284,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="7" r:id="rId4"/>
+    <pivotCache cacheId="6" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -301,7 +301,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="97">
   <si>
     <t>Nama Teknisi</t>
   </si>
@@ -593,12 +593,6 @@
   <si>
     <t>AGUSTUS 2026</t>
   </si>
-  <si>
-    <t>Bagi Hasil Persaudaraan</t>
-  </si>
-  <si>
-    <t>pake omset total yg di pivot proporsional 4-23 agustus</t>
-  </si>
 </sst>
 </file>
 
@@ -618,19 +612,12 @@
     <numFmt numFmtId="172" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="173" formatCode="0.0"/>
   </numFmts>
-  <fonts count="82">
+  <fonts count="81">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1312,413 +1299,413 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="58" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="59" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="57" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="58" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="58" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="59" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="57" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="58" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="58" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="58" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="58" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="60" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="58" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="58" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="58" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="57" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="57" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="57" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0"/>
+    <xf numFmtId="165" fontId="59" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="57" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="57" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="57" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="37" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="36" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="0">
+    <xf numFmtId="41" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="60" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="59" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="74" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="73" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+    <xf numFmtId="171" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+    <xf numFmtId="171" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="80">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-  </cellStyleXfs>
-  <cellXfs count="81">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="50" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="49" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="50" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="49" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="55" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="49" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="49" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="164" fontId="55" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="45" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="44" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="45" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="44" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="54" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="53" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="55" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="56" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="45" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="167" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="55" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="54" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="55" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="164" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="55" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="48" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="166" fontId="47" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="164" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="49" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="17" fontId="48" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="167" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="50" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1">
@@ -1727,7 +1714,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
@@ -1739,48 +1726,47 @@
     <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="144"/>
-    <xf numFmtId="3" fontId="77" fillId="7" borderId="2" xfId="144" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="173" fontId="77" fillId="7" borderId="2" xfId="144" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="77" fillId="7" borderId="2" xfId="144" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="3" xfId="144" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="4" fillId="8" borderId="3" xfId="144" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="173" fontId="4" fillId="0" borderId="3" xfId="144" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="144" applyBorder="1"/>
-    <xf numFmtId="3" fontId="4" fillId="9" borderId="3" xfId="144" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="173" fontId="4" fillId="9" borderId="3" xfId="144" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="144" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="4" fillId="10" borderId="3" xfId="144" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="78" fillId="11" borderId="4" xfId="144" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="144"/>
+    <xf numFmtId="3" fontId="76" fillId="7" borderId="2" xfId="144" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="173" fontId="76" fillId="7" borderId="2" xfId="144" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="76" fillId="7" borderId="2" xfId="144" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="144" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="3" fillId="8" borderId="3" xfId="144" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="173" fontId="3" fillId="0" borderId="3" xfId="144" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="144" applyBorder="1"/>
+    <xf numFmtId="3" fontId="3" fillId="9" borderId="3" xfId="144" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="173" fontId="3" fillId="9" borderId="3" xfId="144" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="3" xfId="144" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="3" fillId="10" borderId="3" xfId="144" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="77" fillId="11" borderId="4" xfId="144" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="78" fillId="12" borderId="4" xfId="144" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="77" fillId="12" borderId="4" xfId="144" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="78" fillId="13" borderId="4" xfId="144" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="77" fillId="13" borderId="4" xfId="144" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="79" fillId="6" borderId="4" xfId="144" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="78" fillId="6" borderId="4" xfId="144" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="144" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="144" applyFill="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="144" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="144" applyFill="1"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="144" applyFont="1"/>
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="144" applyFont="1"/>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="144" applyFont="1"/>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="78" fillId="14" borderId="4" xfId="144" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="77" fillId="14" borderId="4" xfId="144" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="144" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -82691,159 +82677,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{81824E8E-20FA-4468-B922-D7A310F4BD1C}" name="PivotTable9" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A6:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="48">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" numFmtId="169" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="31">
-        <item h="1" x="0"/>
-        <item h="1" x="1"/>
-        <item h="1" x="2"/>
-        <item h="1" x="3"/>
-        <item h="1" x="4"/>
-        <item h="1" x="5"/>
-        <item h="1" x="6"/>
-        <item h="1" x="7"/>
-        <item h="1" x="8"/>
-        <item h="1" x="9"/>
-        <item h="1" x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="8">
-        <item x="2"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="1"/>
-        <item x="6"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="10">
-        <item x="3"/>
-        <item h="1" x="7"/>
-        <item h="1" x="0"/>
-        <item h="1" x="6"/>
-        <item h="1" x="8"/>
-        <item x="2"/>
-        <item h="1" x="1"/>
-        <item h="1" x="5"/>
-        <item h="1" x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="170" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="170" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="170" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" numFmtId="170" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="23"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="19" item="2" hier="-1"/>
-    <pageField fld="1" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Sum of TOTAL HARGA" fld="43" baseField="0" baseItem="0" numFmtId="172"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="2">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{59FAF505-D9FC-4EA1-830E-5FD318966837}" name="PivotTable7" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{59FAF505-D9FC-4EA1-830E-5FD318966837}" name="PivotTable7" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A15:B21" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="48">
     <pivotField showAll="0"/>
@@ -82987,7 +82821,7 @@
     <dataField name="Sum of TOTAL HARGA" fld="43" baseField="0" baseItem="0" numFmtId="172"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="3">
+    <format dxfId="2">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -83003,8 +82837,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6D7241DE-DDB2-4E92-9FF1-D1AD6F5F6399}" name="PivotTable10" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6D7241DE-DDB2-4E92-9FF1-D1AD6F5F6399}" name="PivotTable10" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="D6:E9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="48">
     <pivotField showAll="0"/>
@@ -83040,6 +82874,158 @@
         <item h="1" x="27"/>
         <item h="1" x="28"/>
         <item h="1" x="29"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="8">
+        <item x="2"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="6"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="10">
+        <item x="3"/>
+        <item h="1" x="7"/>
+        <item h="1" x="0"/>
+        <item h="1" x="6"/>
+        <item h="1" x="8"/>
+        <item x="2"/>
+        <item h="1" x="1"/>
+        <item h="1" x="5"/>
+        <item h="1" x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="170" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="170" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="170" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" numFmtId="170" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="23"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="19" item="2" hier="-1"/>
+    <pageField fld="1" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Sum of TOTAL HARGA" fld="43" baseField="0" baseItem="0" numFmtId="172"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="3">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{81824E8E-20FA-4468-B922-D7A310F4BD1C}" name="PivotTable9" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A6:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="48">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" numFmtId="169" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="31">
+        <item h="1" x="0"/>
+        <item h="1" x="1"/>
+        <item h="1" x="2"/>
+        <item h="1" x="3"/>
+        <item h="1" x="4"/>
+        <item h="1" x="5"/>
+        <item h="1" x="6"/>
+        <item h="1" x="7"/>
+        <item h="1" x="8"/>
+        <item h="1" x="9"/>
+        <item h="1" x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -83452,13 +83438,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="53" t="s">
@@ -83652,7 +83638,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11A0FC5D-C99B-4366-885E-56C8D05AE707}">
-  <dimension ref="A1:AH14"/>
+  <dimension ref="A1:AG13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28" style="55" customWidth="1"/>
@@ -83663,70 +83649,67 @@
     <col min="6" max="6" width="18" style="55" customWidth="1"/>
     <col min="7" max="7" width="13" style="55" customWidth="1"/>
     <col min="8" max="8" width="15" style="55" customWidth="1"/>
-    <col min="9" max="10" width="20" style="55" customWidth="1"/>
-    <col min="11" max="11" width="22" style="55" customWidth="1"/>
-    <col min="12" max="12" width="20.140625" style="55" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="23" style="55" customWidth="1"/>
-    <col min="14" max="14" width="18" style="55" customWidth="1"/>
-    <col min="15" max="15" width="20" style="55" customWidth="1"/>
-    <col min="16" max="16" width="21" style="55" customWidth="1"/>
-    <col min="17" max="17" width="16" style="55" customWidth="1"/>
-    <col min="18" max="18" width="12" style="55" customWidth="1"/>
-    <col min="19" max="19" width="11" style="55" customWidth="1"/>
-    <col min="20" max="20" width="17" style="55" customWidth="1"/>
-    <col min="21" max="21" width="13" style="55" customWidth="1"/>
-    <col min="22" max="22" width="17" style="55" customWidth="1"/>
-    <col min="23" max="23" width="15" style="55" customWidth="1"/>
-    <col min="24" max="24" width="22" style="55" customWidth="1"/>
-    <col min="25" max="25" width="27" style="55" customWidth="1"/>
-    <col min="26" max="26" width="28" style="55" customWidth="1"/>
-    <col min="27" max="29" width="16" style="55" customWidth="1"/>
-    <col min="30" max="30" width="14" style="55" customWidth="1"/>
-    <col min="31" max="31" width="17" style="55" customWidth="1"/>
-    <col min="32" max="32" width="26" style="55" customWidth="1"/>
-    <col min="33" max="33" width="18" style="55" customWidth="1"/>
-    <col min="34" max="34" width="24" style="55" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="55"/>
+    <col min="9" max="9" width="20" style="55" customWidth="1"/>
+    <col min="10" max="10" width="22" style="55" customWidth="1"/>
+    <col min="11" max="11" width="20.140625" style="55" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23" style="55" customWidth="1"/>
+    <col min="13" max="13" width="18" style="55" customWidth="1"/>
+    <col min="14" max="14" width="20" style="55" customWidth="1"/>
+    <col min="15" max="15" width="21" style="55" customWidth="1"/>
+    <col min="16" max="16" width="16" style="55" customWidth="1"/>
+    <col min="17" max="17" width="12" style="55" customWidth="1"/>
+    <col min="18" max="18" width="11" style="55" customWidth="1"/>
+    <col min="19" max="19" width="17" style="55" customWidth="1"/>
+    <col min="20" max="20" width="13" style="55" customWidth="1"/>
+    <col min="21" max="21" width="17" style="55" customWidth="1"/>
+    <col min="22" max="22" width="15" style="55" customWidth="1"/>
+    <col min="23" max="23" width="22" style="55" customWidth="1"/>
+    <col min="24" max="24" width="27" style="55" customWidth="1"/>
+    <col min="25" max="25" width="28" style="55" customWidth="1"/>
+    <col min="26" max="28" width="16" style="55" customWidth="1"/>
+    <col min="29" max="29" width="14" style="55" customWidth="1"/>
+    <col min="30" max="30" width="17" style="55" customWidth="1"/>
+    <col min="31" max="31" width="26" style="55" customWidth="1"/>
+    <col min="32" max="32" width="18" style="55" customWidth="1"/>
+    <col min="33" max="33" width="24" style="55" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="55"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="17.25">
+    <row r="1" spans="1:33" ht="17.25">
       <c r="A1" s="74" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="2" spans="1:34">
+    <row r="2" spans="1:33">
       <c r="A2" s="73" t="s">
         <v>94</v>
       </c>
-      <c r="L2" s="72" t="s">
+      <c r="K2" s="72" t="s">
         <v>93</v>
       </c>
-      <c r="M2" s="72" t="s">
+      <c r="L2" s="72" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="3" spans="1:34">
+    <row r="3" spans="1:33">
       <c r="J3" s="71">
-        <v>0.02</v>
+        <v>0.2</v>
       </c>
       <c r="K3" s="71">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="L3" s="71">
+        <v>0.32</v>
+      </c>
+      <c r="M3" s="71">
+        <v>0.6</v>
+      </c>
+      <c r="N3" s="71">
         <v>0.3</v>
       </c>
-      <c r="M3" s="71">
-        <v>0.32</v>
-      </c>
-      <c r="N3" s="71">
-        <v>0.6</v>
-      </c>
-      <c r="O3" s="71">
-        <v>0.3</v>
-      </c>
-      <c r="T3" s="71"/>
+      <c r="S3" s="71"/>
     </row>
-    <row r="4" spans="1:34" ht="15.75" thickBot="1">
+    <row r="4" spans="1:33" ht="15.75" thickBot="1">
       <c r="A4" s="69" t="s">
         <v>0</v>
       </c>
@@ -83755,82 +83738,79 @@
         <v>84</v>
       </c>
       <c r="J4" s="70" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="K4" s="70" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L4" s="70" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M4" s="70" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N4" s="70" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O4" s="70" t="s">
-        <v>79</v>
-      </c>
-      <c r="P4" s="70" t="s">
         <v>78</v>
       </c>
-      <c r="Q4" s="69" t="s">
+      <c r="P4" s="69" t="s">
         <v>77</v>
       </c>
-      <c r="R4" s="69" t="s">
+      <c r="Q4" s="69" t="s">
         <v>76</v>
       </c>
-      <c r="S4" s="69" t="s">
+      <c r="R4" s="69" t="s">
         <v>75</v>
       </c>
-      <c r="T4" s="68" t="s">
+      <c r="S4" s="68" t="s">
         <v>73</v>
       </c>
-      <c r="U4" s="68" t="s">
+      <c r="T4" s="68" t="s">
         <v>44</v>
       </c>
-      <c r="V4" s="68" t="s">
+      <c r="U4" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="W4" s="68" t="s">
+      <c r="V4" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="X4" s="68" t="s">
+      <c r="W4" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="Y4" s="68" t="s">
+      <c r="X4" s="68" t="s">
         <v>54</v>
       </c>
-      <c r="Z4" s="68" t="s">
+      <c r="Y4" s="68" t="s">
         <v>70</v>
       </c>
-      <c r="AA4" s="68" t="s">
+      <c r="Z4" s="68" t="s">
         <v>69</v>
       </c>
-      <c r="AB4" s="68" t="s">
+      <c r="AA4" s="68" t="s">
         <v>68</v>
       </c>
-      <c r="AC4" s="77" t="s">
+      <c r="AB4" s="77" t="s">
         <v>67</v>
       </c>
-      <c r="AD4" s="67" t="s">
+      <c r="AC4" s="67" t="s">
         <v>40</v>
       </c>
-      <c r="AE4" s="67" t="s">
+      <c r="AD4" s="67" t="s">
         <v>4</v>
       </c>
-      <c r="AF4" s="68" t="s">
+      <c r="AE4" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="AG4" s="68" t="s">
+      <c r="AF4" s="68" t="s">
         <v>6</v>
       </c>
-      <c r="AH4" s="67" t="s">
+      <c r="AG4" s="67" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:34">
+    <row r="5" spans="1:33">
       <c r="A5" s="62" t="s">
         <v>45</v>
       </c>
@@ -83858,45 +83838,42 @@
       <c r="I5" s="59">
         <v>40400000</v>
       </c>
-      <c r="J5" s="59" t="e">
-        <f>#REF!*$J$3</f>
-        <v>#REF!</v>
+      <c r="J5" s="59">
+        <f>D5*$J$3</f>
+        <v>2968800</v>
       </c>
       <c r="K5" s="59">
-        <f t="shared" ref="K5:K12" si="0">D5*$K$3</f>
-        <v>2968800</v>
+        <f>E5*$K$3</f>
+        <v>6385200</v>
       </c>
       <c r="L5" s="59">
-        <f>E5*$L$3</f>
-        <v>6385200</v>
+        <f>F5*$L$3</f>
+        <v>1255040</v>
       </c>
       <c r="M5" s="59">
-        <f>F5*$M$3</f>
-        <v>1255040</v>
+        <f>G5*$M$3</f>
+        <v>0</v>
       </c>
       <c r="N5" s="59">
-        <f t="shared" ref="N5:N12" si="1">G5*$N$3</f>
-        <v>0</v>
+        <f>H5*$N$3</f>
+        <v>105000</v>
       </c>
       <c r="O5" s="59">
-        <f t="shared" ref="O5:O12" si="2">H5*$O$3</f>
-        <v>105000</v>
+        <f>SUM(J5:N5)</f>
+        <v>10714040</v>
       </c>
-      <c r="P5" s="59" t="e">
-        <f>SUM(J5:O5)</f>
-        <v>#REF!</v>
+      <c r="P5" s="59">
+        <f>I5*30%</f>
+        <v>12120000</v>
       </c>
       <c r="Q5" s="59">
-        <f t="shared" ref="Q5:Q12" si="3">I5*30%</f>
-        <v>12120000</v>
+        <f t="shared" ref="Q5:Q12" si="0">O5-P5</f>
+        <v>-1405960</v>
       </c>
-      <c r="R5" s="59" t="e">
-        <f t="shared" ref="R5:R12" si="4">P5-Q5</f>
-        <v>#REF!</v>
-      </c>
-      <c r="S5" s="61">
+      <c r="R5" s="61">
         <v>26.5</v>
       </c>
+      <c r="S5" s="60"/>
       <c r="T5" s="60"/>
       <c r="U5" s="60"/>
       <c r="V5" s="60"/>
@@ -83904,29 +83881,28 @@
       <c r="X5" s="60"/>
       <c r="Y5" s="60"/>
       <c r="Z5" s="60"/>
-      <c r="AA5" s="60"/>
-      <c r="AB5" s="60">
+      <c r="AA5" s="60">
+        <v>100000</v>
+      </c>
+      <c r="AB5" s="59">
+        <f t="shared" ref="AB5:AB12" si="1">SUM(S5:AA5)</f>
         <v>100000</v>
       </c>
       <c r="AC5" s="59">
-        <f t="shared" ref="AC5:AC12" si="5">SUM(T5:AB5)</f>
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="AD5" s="59">
-        <v>0</v>
+        <f t="shared" ref="AD5:AD12" si="2">O5-AB5</f>
+        <v>10614040</v>
       </c>
-      <c r="AE5" s="59" t="e">
-        <f t="shared" ref="AE5:AE12" si="6">P5-AC5</f>
-        <v>#REF!</v>
-      </c>
+      <c r="AE5" s="60"/>
       <c r="AF5" s="60"/>
-      <c r="AG5" s="60"/>
-      <c r="AH5" s="59">
-        <f t="shared" ref="AH5:AH12" si="7">AF5+AG5</f>
+      <c r="AG5" s="59">
+        <f t="shared" ref="AG5:AG12" si="3">AE5+AF5</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34">
+    <row r="6" spans="1:33">
       <c r="A6" s="65" t="s">
         <v>50</v>
       </c>
@@ -83954,77 +83930,73 @@
       <c r="I6" s="63">
         <v>34123500</v>
       </c>
-      <c r="J6" s="59" t="e">
-        <f>#REF!*$J$3</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K6" s="59">
-        <f t="shared" si="0"/>
+      <c r="J6" s="59">
+        <f>D6*$J$3</f>
         <v>1992700</v>
       </c>
-      <c r="L6" s="66">
+      <c r="K6" s="66">
         <f>E6*35.5%</f>
         <v>3883345</v>
       </c>
-      <c r="M6" s="66">
+      <c r="L6" s="66">
         <f>F6*37.5%</f>
         <v>2050875</v>
       </c>
-      <c r="N6" s="59">
-        <f t="shared" si="1"/>
+      <c r="M6" s="59">
+        <f>G6*$M$3</f>
         <v>0</v>
       </c>
-      <c r="O6" s="59">
-        <f t="shared" si="2"/>
+      <c r="N6" s="59">
+        <f>H6*$N$3</f>
         <v>2325600</v>
       </c>
-      <c r="P6" s="59" t="e">
-        <f t="shared" ref="P6:P12" si="8">SUM(J6:O6)</f>
-        <v>#REF!</v>
+      <c r="O6" s="59">
+        <f>SUM(J6:N6)</f>
+        <v>10252520</v>
+      </c>
+      <c r="P6" s="59">
+        <f>I6*30%</f>
+        <v>10237050</v>
       </c>
       <c r="Q6" s="59">
-        <f t="shared" si="3"/>
-        <v>10237050</v>
+        <f t="shared" si="0"/>
+        <v>15470</v>
       </c>
-      <c r="R6" s="59" t="e">
-        <f t="shared" si="4"/>
-        <v>#REF!</v>
-      </c>
-      <c r="S6" s="64">
+      <c r="R6" s="64">
         <v>30</v>
       </c>
+      <c r="S6" s="60"/>
       <c r="T6" s="60"/>
-      <c r="U6" s="60"/>
-      <c r="V6" s="60">
+      <c r="U6" s="60">
         <v>343805</v>
       </c>
+      <c r="V6" s="60"/>
       <c r="W6" s="60"/>
       <c r="X6" s="60"/>
       <c r="Y6" s="60"/>
       <c r="Z6" s="60"/>
-      <c r="AA6" s="60"/>
-      <c r="AB6" s="60">
+      <c r="AA6" s="60">
         <v>100000</v>
       </c>
-      <c r="AC6" s="63">
-        <f t="shared" si="5"/>
+      <c r="AB6" s="63">
+        <f t="shared" si="1"/>
         <v>443805</v>
       </c>
-      <c r="AD6" s="59">
+      <c r="AC6" s="59">
         <v>0</v>
       </c>
-      <c r="AE6" s="59" t="e">
-        <f t="shared" si="6"/>
-        <v>#REF!</v>
+      <c r="AD6" s="59">
+        <f t="shared" si="2"/>
+        <v>9808715</v>
       </c>
+      <c r="AE6" s="60"/>
       <c r="AF6" s="60"/>
-      <c r="AG6" s="60"/>
-      <c r="AH6" s="63">
-        <f t="shared" si="7"/>
+      <c r="AG6" s="63">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:34">
+    <row r="7" spans="1:33">
       <c r="A7" s="62" t="s">
         <v>71</v>
       </c>
@@ -84052,78 +84024,74 @@
       <c r="I7" s="59">
         <v>31339000</v>
       </c>
-      <c r="J7" s="59" t="e">
-        <f>#REF!*$J$3</f>
-        <v>#REF!</v>
+      <c r="J7" s="59">
+        <f>D7*$J$3</f>
+        <v>2651400</v>
       </c>
       <c r="K7" s="59">
-        <f t="shared" si="0"/>
-        <v>2651400</v>
+        <f>E7*$K$3</f>
+        <v>2586000</v>
       </c>
       <c r="L7" s="59">
-        <f t="shared" ref="L7:L12" si="9">E7*$L$3</f>
-        <v>2586000</v>
+        <f>F7*$L$3</f>
+        <v>3027840</v>
       </c>
       <c r="M7" s="59">
-        <f t="shared" ref="M7:M12" si="10">F7*$M$3</f>
-        <v>3027840</v>
+        <f>G7*$M$3</f>
+        <v>0</v>
       </c>
       <c r="N7" s="59">
-        <f t="shared" si="1"/>
+        <f>H7*$N$3</f>
         <v>0</v>
       </c>
       <c r="O7" s="59">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f>SUM(J7:N7)</f>
+        <v>8265240</v>
       </c>
-      <c r="P7" s="59" t="e">
-        <f t="shared" si="8"/>
-        <v>#REF!</v>
+      <c r="P7" s="59">
+        <f>I7*30%</f>
+        <v>9401700</v>
       </c>
       <c r="Q7" s="59">
-        <f t="shared" si="3"/>
-        <v>9401700</v>
+        <f t="shared" si="0"/>
+        <v>-1136460</v>
       </c>
-      <c r="R7" s="59" t="e">
-        <f t="shared" si="4"/>
-        <v>#REF!</v>
-      </c>
-      <c r="S7" s="61">
+      <c r="R7" s="61">
         <v>26.4</v>
       </c>
-      <c r="T7" s="60">
+      <c r="S7" s="60">
         <f>281000*30%</f>
         <v>84300</v>
       </c>
+      <c r="T7" s="60"/>
       <c r="U7" s="60"/>
       <c r="V7" s="60"/>
       <c r="W7" s="60"/>
       <c r="X7" s="60"/>
       <c r="Y7" s="60"/>
       <c r="Z7" s="60"/>
-      <c r="AA7" s="60"/>
-      <c r="AB7" s="60">
+      <c r="AA7" s="60">
         <v>100000</v>
       </c>
-      <c r="AC7" s="59">
-        <f t="shared" si="5"/>
+      <c r="AB7" s="59">
+        <f t="shared" si="1"/>
         <v>184300</v>
       </c>
-      <c r="AD7" s="59">
+      <c r="AC7" s="59">
         <v>0</v>
       </c>
-      <c r="AE7" s="59" t="e">
-        <f t="shared" si="6"/>
-        <v>#REF!</v>
+      <c r="AD7" s="59">
+        <f t="shared" si="2"/>
+        <v>8080940</v>
       </c>
+      <c r="AE7" s="60"/>
       <c r="AF7" s="60"/>
-      <c r="AG7" s="60"/>
-      <c r="AH7" s="59">
-        <f t="shared" si="7"/>
+      <c r="AG7" s="59">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:34">
+    <row r="8" spans="1:33">
       <c r="A8" s="65" t="s">
         <v>51</v>
       </c>
@@ -84151,83 +84119,79 @@
       <c r="I8" s="63">
         <v>23312000</v>
       </c>
-      <c r="J8" s="59" t="e">
-        <f>#REF!*$J$3</f>
-        <v>#REF!</v>
+      <c r="J8" s="59">
+        <f>D8*$J$3</f>
+        <v>2298600</v>
       </c>
       <c r="K8" s="59">
-        <f t="shared" si="0"/>
-        <v>2298600</v>
+        <f>E8*$K$3</f>
+        <v>3146400</v>
       </c>
       <c r="L8" s="59">
-        <f t="shared" si="9"/>
-        <v>3146400</v>
+        <f>F8*$L$3</f>
+        <v>425920</v>
       </c>
       <c r="M8" s="59">
-        <f t="shared" si="10"/>
-        <v>425920</v>
+        <f>G8*$M$3</f>
+        <v>0</v>
       </c>
       <c r="N8" s="59">
-        <f t="shared" si="1"/>
+        <f>H8*$N$3</f>
         <v>0</v>
       </c>
       <c r="O8" s="59">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f>SUM(J8:N8)</f>
+        <v>5870920</v>
       </c>
-      <c r="P8" s="59" t="e">
-        <f t="shared" si="8"/>
-        <v>#REF!</v>
+      <c r="P8" s="59">
+        <f>I8*30%</f>
+        <v>6993600</v>
       </c>
       <c r="Q8" s="59">
-        <f t="shared" si="3"/>
-        <v>6993600</v>
+        <f t="shared" si="0"/>
+        <v>-1122680</v>
       </c>
-      <c r="R8" s="59" t="e">
-        <f t="shared" si="4"/>
-        <v>#REF!</v>
-      </c>
-      <c r="S8" s="64">
+      <c r="R8" s="64">
         <v>25.2</v>
       </c>
-      <c r="T8" s="60">
+      <c r="S8" s="60">
         <f>200000*30%</f>
         <v>60000</v>
       </c>
+      <c r="T8" s="60"/>
       <c r="U8" s="60"/>
       <c r="V8" s="60"/>
       <c r="W8" s="60"/>
       <c r="X8" s="60"/>
       <c r="Y8" s="60"/>
       <c r="Z8" s="60"/>
-      <c r="AA8" s="60"/>
-      <c r="AB8" s="60">
+      <c r="AA8" s="60">
         <v>100000</v>
       </c>
-      <c r="AC8" s="63">
-        <f t="shared" si="5"/>
+      <c r="AB8" s="63">
+        <f t="shared" si="1"/>
         <v>160000</v>
       </c>
-      <c r="AD8" s="59">
+      <c r="AC8" s="59">
         <v>0</v>
       </c>
-      <c r="AE8" s="59" t="e">
-        <f t="shared" si="6"/>
-        <v>#REF!</v>
+      <c r="AD8" s="59">
+        <f t="shared" si="2"/>
+        <v>5710920</v>
       </c>
-      <c r="AF8" s="60">
+      <c r="AE8" s="60">
         <f>I8*5%</f>
         <v>1165600</v>
       </c>
-      <c r="AG8" s="60">
+      <c r="AF8" s="60">
         <v>51560605.149999999</v>
       </c>
-      <c r="AH8" s="63">
-        <f t="shared" si="7"/>
+      <c r="AG8" s="63">
+        <f t="shared" si="3"/>
         <v>52726205.149999999</v>
       </c>
     </row>
-    <row r="9" spans="1:34">
+    <row r="9" spans="1:33">
       <c r="A9" s="62" t="s">
         <v>74</v>
       </c>
@@ -84256,78 +84220,75 @@
         <v>18766000</v>
       </c>
       <c r="J9" s="59">
+        <f>D9*$J$3</f>
+        <v>2727200</v>
+      </c>
+      <c r="K9" s="59">
+        <f>E9*$K$3</f>
+        <v>1319700</v>
+      </c>
+      <c r="L9" s="59">
+        <f>F9*$L$3</f>
         <v>0</v>
       </c>
-      <c r="K9" s="59">
-        <f t="shared" si="0"/>
-        <v>2727200</v>
-      </c>
-      <c r="L9" s="59">
-        <f t="shared" si="9"/>
-        <v>1319700</v>
-      </c>
       <c r="M9" s="59">
-        <f t="shared" si="10"/>
+        <f>G9*$M$3</f>
         <v>0</v>
       </c>
       <c r="N9" s="59">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>H9*$N$3</f>
+        <v>219300</v>
       </c>
       <c r="O9" s="59">
-        <f t="shared" si="2"/>
-        <v>219300</v>
+        <f>SUM(J9:N9)</f>
+        <v>4266200</v>
       </c>
       <c r="P9" s="59">
-        <f t="shared" si="8"/>
-        <v>4266200</v>
+        <f>I9*30%</f>
+        <v>5629800</v>
       </c>
       <c r="Q9" s="59">
-        <f t="shared" si="3"/>
-        <v>5629800</v>
-      </c>
-      <c r="R9" s="59">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>-1363600</v>
       </c>
-      <c r="S9" s="61">
+      <c r="R9" s="61">
         <v>22.7</v>
       </c>
-      <c r="T9" s="60">
+      <c r="S9" s="60">
         <f>135000*20%</f>
         <v>27000</v>
       </c>
+      <c r="T9" s="60"/>
       <c r="U9" s="60"/>
       <c r="V9" s="60"/>
       <c r="W9" s="60"/>
       <c r="X9" s="60"/>
-      <c r="Y9" s="60"/>
-      <c r="Z9" s="60">
+      <c r="Y9" s="60">
         <v>30000</v>
       </c>
-      <c r="AA9" s="60">
+      <c r="Z9" s="60">
         <v>100000</v>
       </c>
-      <c r="AB9" s="60"/>
-      <c r="AC9" s="59">
-        <f t="shared" si="5"/>
+      <c r="AA9" s="60"/>
+      <c r="AB9" s="59">
+        <f t="shared" si="1"/>
         <v>157000</v>
       </c>
-      <c r="AD9" s="59">
+      <c r="AC9" s="59">
         <v>0</v>
       </c>
-      <c r="AE9" s="59">
-        <f t="shared" si="6"/>
+      <c r="AD9" s="59">
+        <f t="shared" si="2"/>
         <v>4109200</v>
       </c>
+      <c r="AE9" s="60"/>
       <c r="AF9" s="60"/>
-      <c r="AG9" s="60"/>
-      <c r="AH9" s="59">
-        <f t="shared" si="7"/>
+      <c r="AG9" s="59">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:34">
+    <row r="10" spans="1:33">
       <c r="A10" s="65" t="s">
         <v>52</v>
       </c>
@@ -84355,77 +84316,74 @@
       <c r="I10" s="63">
         <v>17151250</v>
       </c>
-      <c r="J10" s="63">
+      <c r="J10" s="59">
+        <f>D10*$J$3</f>
+        <v>1987150</v>
+      </c>
+      <c r="K10" s="59">
+        <f>E10*$K$3</f>
+        <v>1936650</v>
+      </c>
+      <c r="L10" s="59">
+        <f>F10*$L$3</f>
+        <v>43200</v>
+      </c>
+      <c r="M10" s="59">
+        <f>G10*$M$3</f>
         <v>0</v>
       </c>
-      <c r="K10" s="59">
-        <f t="shared" si="0"/>
-        <v>1987150</v>
-      </c>
-      <c r="L10" s="59">
-        <f t="shared" si="9"/>
-        <v>1936650</v>
-      </c>
-      <c r="M10" s="59">
-        <f t="shared" si="10"/>
-        <v>43200</v>
-      </c>
       <c r="N10" s="59">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>H10*$N$3</f>
+        <v>187500</v>
       </c>
       <c r="O10" s="59">
-        <f t="shared" si="2"/>
-        <v>187500</v>
+        <f>SUM(J10:N10)</f>
+        <v>4154500</v>
       </c>
       <c r="P10" s="59">
-        <f t="shared" si="8"/>
-        <v>4154500</v>
+        <f>I10*30%</f>
+        <v>5145375</v>
       </c>
       <c r="Q10" s="59">
-        <f t="shared" si="3"/>
-        <v>5145375</v>
-      </c>
-      <c r="R10" s="59">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>-990875</v>
       </c>
-      <c r="S10" s="64">
+      <c r="R10" s="64">
         <v>24.2</v>
       </c>
-      <c r="T10" s="60">
+      <c r="S10" s="60">
         <f>400000*30%</f>
         <v>120000</v>
       </c>
+      <c r="T10" s="60"/>
       <c r="U10" s="60"/>
       <c r="V10" s="60"/>
       <c r="W10" s="60"/>
       <c r="X10" s="60"/>
       <c r="Y10" s="60"/>
       <c r="Z10" s="60"/>
-      <c r="AA10" s="60"/>
-      <c r="AB10" s="60">
+      <c r="AA10" s="60">
         <v>100000</v>
       </c>
-      <c r="AC10" s="63">
-        <f t="shared" si="5"/>
+      <c r="AB10" s="63">
+        <f t="shared" si="1"/>
         <v>220000</v>
       </c>
-      <c r="AD10" s="59">
+      <c r="AC10" s="59">
         <v>0</v>
       </c>
-      <c r="AE10" s="59">
-        <f t="shared" si="6"/>
+      <c r="AD10" s="59">
+        <f t="shared" si="2"/>
         <v>3934500</v>
       </c>
+      <c r="AE10" s="60"/>
       <c r="AF10" s="60"/>
-      <c r="AG10" s="60"/>
-      <c r="AH10" s="63">
-        <f t="shared" si="7"/>
+      <c r="AG10" s="63">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:34">
+    <row r="11" spans="1:33">
       <c r="A11" s="62" t="s">
         <v>46</v>
       </c>
@@ -84454,47 +84412,45 @@
         <v>331000</v>
       </c>
       <c r="J11" s="59">
+        <f>D11*$J$3</f>
         <v>0</v>
       </c>
       <c r="K11" s="59">
+        <f>E11*$K$3</f>
+        <v>99300</v>
+      </c>
+      <c r="L11" s="59">
+        <f>F11*$L$3</f>
+        <v>0</v>
+      </c>
+      <c r="M11" s="59">
+        <f>G11*$M$3</f>
+        <v>0</v>
+      </c>
+      <c r="N11" s="59">
+        <f>H11*$N$3</f>
+        <v>0</v>
+      </c>
+      <c r="O11" s="59">
+        <f>SUM(J11:N11)</f>
+        <v>99300</v>
+      </c>
+      <c r="P11" s="59">
+        <f>I11*30%</f>
+        <v>99300</v>
+      </c>
+      <c r="Q11" s="59">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L11" s="59">
-        <f t="shared" si="9"/>
-        <v>99300</v>
-      </c>
-      <c r="M11" s="59">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="N11" s="59">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="O11" s="59">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="P11" s="59">
-        <f t="shared" si="8"/>
-        <v>99300</v>
-      </c>
-      <c r="Q11" s="59">
-        <f t="shared" si="3"/>
-        <v>99300</v>
-      </c>
-      <c r="R11" s="59">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S11" s="61">
+      <c r="R11" s="61">
         <v>30</v>
       </c>
-      <c r="T11" s="60">
+      <c r="S11" s="60">
         <f>175000*30%</f>
         <v>52500</v>
       </c>
+      <c r="T11" s="60"/>
       <c r="U11" s="60"/>
       <c r="V11" s="60"/>
       <c r="W11" s="60"/>
@@ -84502,26 +84458,25 @@
       <c r="Y11" s="60"/>
       <c r="Z11" s="60"/>
       <c r="AA11" s="60"/>
-      <c r="AB11" s="60"/>
-      <c r="AC11" s="59">
-        <f t="shared" si="5"/>
+      <c r="AB11" s="59">
+        <f t="shared" si="1"/>
         <v>52500</v>
       </c>
-      <c r="AD11" s="59">
+      <c r="AC11" s="59">
         <v>0</v>
       </c>
-      <c r="AE11" s="59">
-        <f t="shared" si="6"/>
+      <c r="AD11" s="59">
+        <f t="shared" si="2"/>
         <v>46800</v>
       </c>
+      <c r="AE11" s="60"/>
       <c r="AF11" s="60"/>
-      <c r="AG11" s="60"/>
-      <c r="AH11" s="59">
-        <f t="shared" si="7"/>
+      <c r="AG11" s="59">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:34" ht="15.75" thickBot="1">
+    <row r="12" spans="1:33" ht="15.75" thickBot="1">
       <c r="A12" s="62" t="s">
         <v>72</v>
       </c>
@@ -84550,43 +84505,41 @@
         <v>150000</v>
       </c>
       <c r="J12" s="59">
+        <f>D12*$J$3</f>
+        <v>30000</v>
+      </c>
+      <c r="K12" s="59">
+        <f>E12*$K$3</f>
         <v>0</v>
       </c>
-      <c r="K12" s="59">
-        <f t="shared" si="0"/>
-        <v>30000</v>
-      </c>
       <c r="L12" s="59">
-        <f t="shared" si="9"/>
+        <f>F12*$L$3</f>
         <v>0</v>
       </c>
       <c r="M12" s="59">
-        <f t="shared" si="10"/>
+        <f>G12*$M$3</f>
         <v>0</v>
       </c>
       <c r="N12" s="59">
-        <f t="shared" si="1"/>
+        <f>H12*$N$3</f>
         <v>0</v>
       </c>
       <c r="O12" s="59">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f>SUM(J12:N12)</f>
+        <v>30000</v>
       </c>
       <c r="P12" s="59">
-        <f t="shared" si="8"/>
-        <v>30000</v>
+        <f>I12*30%</f>
+        <v>45000</v>
       </c>
       <c r="Q12" s="59">
-        <f t="shared" si="3"/>
-        <v>45000</v>
-      </c>
-      <c r="R12" s="59">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>-15000</v>
       </c>
-      <c r="S12" s="61">
+      <c r="R12" s="61">
         <v>20</v>
       </c>
+      <c r="S12" s="60"/>
       <c r="T12" s="60"/>
       <c r="U12" s="60"/>
       <c r="V12" s="60"/>
@@ -84595,159 +84548,152 @@
       <c r="Y12" s="60"/>
       <c r="Z12" s="60"/>
       <c r="AA12" s="60"/>
-      <c r="AB12" s="60"/>
+      <c r="AB12" s="59">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="AC12" s="59">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AD12" s="59">
-        <v>0</v>
-      </c>
-      <c r="AE12" s="59">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>30000</v>
       </c>
+      <c r="AE12" s="60"/>
       <c r="AF12" s="60"/>
-      <c r="AG12" s="60"/>
-      <c r="AH12" s="59">
-        <f t="shared" si="7"/>
+      <c r="AG12" s="59">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:34">
+    <row r="13" spans="1:33">
       <c r="A13" s="58" t="s">
         <v>28</v>
       </c>
       <c r="B13" s="58"/>
       <c r="C13" s="56">
-        <f t="shared" ref="C13:R13" si="11">SUM(C5:C12)</f>
+        <f t="shared" ref="C13:Q13" si="4">SUM(C5:C12)</f>
         <v>582</v>
       </c>
       <c r="D13" s="56">
-        <f t="shared" si="11"/>
+        <f t="shared" si="4"/>
         <v>73279250</v>
       </c>
       <c r="E13" s="56">
-        <f t="shared" si="11"/>
+        <f t="shared" si="4"/>
         <v>62516500</v>
       </c>
       <c r="F13" s="56">
-        <f t="shared" si="11"/>
+        <f t="shared" si="4"/>
         <v>20319000</v>
       </c>
       <c r="G13" s="56">
-        <f t="shared" si="11"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H13" s="56">
-        <f t="shared" si="11"/>
+        <f t="shared" si="4"/>
         <v>9458000</v>
       </c>
       <c r="I13" s="56">
-        <f t="shared" si="11"/>
+        <f t="shared" si="4"/>
         <v>165572750</v>
       </c>
-      <c r="J13" s="56"/>
-      <c r="K13" s="56">
-        <f t="shared" si="11"/>
+      <c r="J13" s="56">
+        <f t="shared" si="4"/>
         <v>14655850</v>
       </c>
-      <c r="L13" s="56">
-        <f t="shared" si="11"/>
+      <c r="K13" s="56">
+        <f t="shared" si="4"/>
         <v>19356595</v>
       </c>
-      <c r="M13" s="56">
-        <f t="shared" si="11"/>
+      <c r="L13" s="56">
+        <f t="shared" si="4"/>
         <v>6802875</v>
       </c>
-      <c r="N13" s="56">
-        <f t="shared" si="11"/>
+      <c r="M13" s="56">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O13" s="56">
-        <f t="shared" si="11"/>
+      <c r="N13" s="56">
+        <f t="shared" si="4"/>
         <v>2837400</v>
       </c>
-      <c r="P13" s="56" t="e">
-        <f t="shared" si="11"/>
-        <v>#REF!</v>
+      <c r="O13" s="56">
+        <f t="shared" si="4"/>
+        <v>43652720</v>
+      </c>
+      <c r="P13" s="56">
+        <f t="shared" si="4"/>
+        <v>49671825</v>
       </c>
       <c r="Q13" s="56">
-        <f t="shared" si="11"/>
-        <v>49671825</v>
+        <f t="shared" si="4"/>
+        <v>-6019105</v>
       </c>
-      <c r="R13" s="56" t="e">
-        <f t="shared" si="11"/>
-        <v>#REF!</v>
+      <c r="R13" s="57">
+        <f>IF(I13=0,0,O13/I13*100)</f>
+        <v>26.364676554565889</v>
       </c>
-      <c r="S13" s="57" t="e">
-        <f>IF(I13=0,0,P13/I13*100)</f>
-        <v>#REF!</v>
+      <c r="S13" s="56">
+        <f t="shared" ref="S13:AG13" si="5">SUM(S5:S12)</f>
+        <v>343800</v>
       </c>
       <c r="T13" s="56">
-        <f t="shared" ref="T13:AH13" si="12">SUM(T5:T12)</f>
-        <v>343800</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="U13" s="56">
-        <f t="shared" si="12"/>
+        <f t="shared" si="5"/>
+        <v>343805</v>
+      </c>
+      <c r="V13" s="56">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="V13" s="56">
-        <f t="shared" si="12"/>
-        <v>343805</v>
-      </c>
       <c r="W13" s="56">
-        <f t="shared" si="12"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="X13" s="56">
-        <f t="shared" si="12"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Y13" s="56">
-        <f t="shared" si="12"/>
+        <f t="shared" si="5"/>
+        <v>30000</v>
+      </c>
+      <c r="Z13" s="56">
+        <f t="shared" si="5"/>
+        <v>100000</v>
+      </c>
+      <c r="AA13" s="56">
+        <f t="shared" si="5"/>
+        <v>500000</v>
+      </c>
+      <c r="AB13" s="56">
+        <f t="shared" si="5"/>
+        <v>1317605</v>
+      </c>
+      <c r="AC13" s="56">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Z13" s="56">
-        <f t="shared" si="12"/>
-        <v>30000</v>
+      <c r="AD13" s="56">
+        <f t="shared" si="5"/>
+        <v>42335115</v>
       </c>
-      <c r="AA13" s="56">
-        <f t="shared" si="12"/>
-        <v>100000</v>
-      </c>
-      <c r="AB13" s="56">
-        <f t="shared" si="12"/>
-        <v>500000</v>
-      </c>
-      <c r="AC13" s="56">
-        <f t="shared" si="12"/>
-        <v>1317605</v>
-      </c>
-      <c r="AD13" s="56">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AE13" s="56" t="e">
-        <f t="shared" si="12"/>
-        <v>#REF!</v>
+      <c r="AE13" s="56">
+        <f t="shared" si="5"/>
+        <v>1165600</v>
       </c>
       <c r="AF13" s="56">
-        <f t="shared" si="12"/>
-        <v>1165600</v>
+        <f t="shared" si="5"/>
+        <v>51560605.149999999</v>
       </c>
       <c r="AG13" s="56">
-        <f t="shared" si="12"/>
-        <v>51560605.149999999</v>
-      </c>
-      <c r="AH13" s="56">
-        <f t="shared" si="12"/>
+        <f t="shared" si="5"/>
         <v>52726205.149999999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:34">
-      <c r="J14" s="78" t="s">
-        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -85056,61 +85002,61 @@
         <f>RAW!I5</f>
         <v>40400000</v>
       </c>
-      <c r="M8" s="29" t="e">
-        <f>RAW!P5</f>
-        <v>#REF!</v>
+      <c r="M8" s="29">
+        <f>RAW!O5</f>
+        <v>10714040</v>
       </c>
       <c r="N8" s="30">
-        <f>RAW!AD5</f>
+        <f>RAW!AC5</f>
         <v>0</v>
       </c>
-      <c r="O8" s="31" t="e">
+      <c r="O8" s="31">
         <f t="shared" ref="O8:O15" si="1">SUM(M8:N8)</f>
-        <v>#REF!</v>
+        <v>10714040</v>
       </c>
       <c r="P8" s="31">
+        <f>RAW!S5</f>
+        <v>0</v>
+      </c>
+      <c r="Q8" s="31">
         <f>RAW!T5</f>
         <v>0</v>
       </c>
-      <c r="Q8" s="31">
+      <c r="R8" s="31">
         <f>RAW!U5</f>
         <v>0</v>
       </c>
-      <c r="R8" s="31">
+      <c r="S8" s="31">
         <f>RAW!V5</f>
         <v>0</v>
       </c>
-      <c r="S8" s="31">
+      <c r="T8" s="31">
         <f>RAW!W5</f>
         <v>0</v>
       </c>
-      <c r="T8" s="31">
+      <c r="U8" s="31">
         <f>RAW!X5</f>
         <v>0</v>
       </c>
-      <c r="U8" s="31">
+      <c r="V8" s="31">
         <f>RAW!Y5</f>
         <v>0</v>
       </c>
-      <c r="V8" s="31">
+      <c r="W8" s="31">
         <f>RAW!Z5</f>
         <v>0</v>
       </c>
-      <c r="W8" s="31">
+      <c r="X8" s="31">
         <f>RAW!AA5</f>
-        <v>0</v>
+        <v>100000</v>
       </c>
-      <c r="X8" s="31">
+      <c r="Y8" s="31">
         <f>RAW!AB5</f>
         <v>100000</v>
       </c>
-      <c r="Y8" s="31">
-        <f>RAW!AC5</f>
-        <v>100000</v>
-      </c>
-      <c r="Z8" s="31" t="e">
+      <c r="Z8" s="31">
         <f>O8-Y8</f>
-        <v>#REF!</v>
+        <v>10614040</v>
       </c>
       <c r="AA8" s="37" t="str">
         <f>_xlfn.TEXTJOIN(" | ",TRUE,IF(V8&gt;0,"Biaya Pendaftaran Koperasi: "&amp;TEXT(V8,"#.##0"),""),IF(W8&gt;0,"Simpanan Pokok: "&amp;TEXT(W8,"#.##0"),""),IF(X8&gt;0,"Simpanan Wajib: "&amp;TEXT(X8,"#.##0"),""))</f>
@@ -85149,61 +85095,61 @@
         <f>RAW!I6</f>
         <v>34123500</v>
       </c>
-      <c r="M9" s="29" t="e">
-        <f>RAW!P6</f>
-        <v>#REF!</v>
+      <c r="M9" s="29">
+        <f>RAW!O6</f>
+        <v>10252520</v>
       </c>
       <c r="N9" s="30">
-        <f>RAW!AD6</f>
+        <f>RAW!AC6</f>
         <v>0</v>
       </c>
-      <c r="O9" s="31" t="e">
+      <c r="O9" s="31">
         <f t="shared" si="1"/>
-        <v>#REF!</v>
+        <v>10252520</v>
       </c>
       <c r="P9" s="31">
+        <f>RAW!S6</f>
+        <v>0</v>
+      </c>
+      <c r="Q9" s="31">
         <f>RAW!T6</f>
         <v>0</v>
       </c>
-      <c r="Q9" s="31">
+      <c r="R9" s="31">
         <f>RAW!U6</f>
-        <v>0</v>
-      </c>
-      <c r="R9" s="31">
-        <f>RAW!V6</f>
         <v>343805</v>
       </c>
       <c r="S9" s="31">
+        <f>RAW!V6</f>
+        <v>0</v>
+      </c>
+      <c r="T9" s="31">
         <f>RAW!W6</f>
         <v>0</v>
       </c>
-      <c r="T9" s="31">
+      <c r="U9" s="31">
         <f>RAW!X6</f>
         <v>0</v>
       </c>
-      <c r="U9" s="31">
+      <c r="V9" s="31">
         <f>RAW!Y6</f>
         <v>0</v>
       </c>
-      <c r="V9" s="31">
+      <c r="W9" s="31">
         <f>RAW!Z6</f>
         <v>0</v>
       </c>
-      <c r="W9" s="31">
+      <c r="X9" s="31">
         <f>RAW!AA6</f>
-        <v>0</v>
-      </c>
-      <c r="X9" s="31">
-        <f>RAW!AB6</f>
         <v>100000</v>
       </c>
       <c r="Y9" s="31">
-        <f>RAW!AC6</f>
+        <f>RAW!AB6</f>
         <v>443805</v>
       </c>
-      <c r="Z9" s="31" t="e">
+      <c r="Z9" s="31">
         <f t="shared" ref="Z9:Z15" si="2">O9-Y9</f>
-        <v>#REF!</v>
+        <v>9808715</v>
       </c>
       <c r="AA9" s="37" t="str">
         <f t="shared" ref="AA9:AA15" si="3">_xlfn.TEXTJOIN(" | ",TRUE,IF(V9&gt;0,"Biaya Pendaftaran Koperasi: "&amp;TEXT(V9,"#.##0"),""),IF(W9&gt;0,"Simpanan Pokok: "&amp;TEXT(W9,"#.##0"),""),IF(X9&gt;0,"Simpanan Wajib: "&amp;TEXT(X9,"#.##0"),""))</f>
@@ -85242,61 +85188,61 @@
         <f>RAW!I7</f>
         <v>31339000</v>
       </c>
-      <c r="M10" s="29" t="e">
-        <f>RAW!P7</f>
-        <v>#REF!</v>
+      <c r="M10" s="29">
+        <f>RAW!O7</f>
+        <v>8265240</v>
       </c>
       <c r="N10" s="30">
-        <f>RAW!AD7</f>
+        <f>RAW!AC7</f>
         <v>0</v>
       </c>
-      <c r="O10" s="31" t="e">
+      <c r="O10" s="31">
         <f t="shared" si="1"/>
-        <v>#REF!</v>
+        <v>8265240</v>
       </c>
       <c r="P10" s="31">
-        <f>RAW!T7</f>
+        <f>RAW!S7</f>
         <v>84300</v>
       </c>
       <c r="Q10" s="31">
+        <f>RAW!T7</f>
+        <v>0</v>
+      </c>
+      <c r="R10" s="31">
         <f>RAW!U7</f>
         <v>0</v>
       </c>
-      <c r="R10" s="31">
+      <c r="S10" s="31">
         <f>RAW!V7</f>
         <v>0</v>
       </c>
-      <c r="S10" s="31">
+      <c r="T10" s="31">
         <f>RAW!W7</f>
         <v>0</v>
       </c>
-      <c r="T10" s="31">
+      <c r="U10" s="31">
         <f>RAW!X7</f>
         <v>0</v>
       </c>
-      <c r="U10" s="31">
+      <c r="V10" s="31">
         <f>RAW!Y7</f>
         <v>0</v>
       </c>
-      <c r="V10" s="31">
+      <c r="W10" s="31">
         <f>RAW!Z7</f>
         <v>0</v>
       </c>
-      <c r="W10" s="31">
+      <c r="X10" s="31">
         <f>RAW!AA7</f>
-        <v>0</v>
-      </c>
-      <c r="X10" s="31">
-        <f>RAW!AB7</f>
         <v>100000</v>
       </c>
       <c r="Y10" s="31">
-        <f>RAW!AC7</f>
+        <f>RAW!AB7</f>
         <v>184300</v>
       </c>
-      <c r="Z10" s="31" t="e">
+      <c r="Z10" s="31">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>8080940</v>
       </c>
       <c r="AA10" s="37" t="str">
         <f t="shared" si="3"/>
@@ -85335,61 +85281,61 @@
         <f>RAW!I8</f>
         <v>23312000</v>
       </c>
-      <c r="M11" s="29" t="e">
-        <f>RAW!P8</f>
-        <v>#REF!</v>
+      <c r="M11" s="29">
+        <f>RAW!O8</f>
+        <v>5870920</v>
       </c>
       <c r="N11" s="30">
-        <f>RAW!AD8</f>
+        <f>RAW!AC8</f>
         <v>0</v>
       </c>
-      <c r="O11" s="31" t="e">
+      <c r="O11" s="31">
         <f t="shared" si="1"/>
-        <v>#REF!</v>
+        <v>5870920</v>
       </c>
       <c r="P11" s="31">
-        <f>RAW!T8</f>
+        <f>RAW!S8</f>
         <v>60000</v>
       </c>
       <c r="Q11" s="31">
+        <f>RAW!T8</f>
+        <v>0</v>
+      </c>
+      <c r="R11" s="31">
         <f>RAW!U8</f>
         <v>0</v>
       </c>
-      <c r="R11" s="31">
+      <c r="S11" s="31">
         <f>RAW!V8</f>
         <v>0</v>
       </c>
-      <c r="S11" s="31">
+      <c r="T11" s="31">
         <f>RAW!W8</f>
         <v>0</v>
       </c>
-      <c r="T11" s="31">
+      <c r="U11" s="31">
         <f>RAW!X8</f>
         <v>0</v>
       </c>
-      <c r="U11" s="31">
+      <c r="V11" s="31">
         <f>RAW!Y8</f>
         <v>0</v>
       </c>
-      <c r="V11" s="31">
+      <c r="W11" s="31">
         <f>RAW!Z8</f>
         <v>0</v>
       </c>
-      <c r="W11" s="31">
+      <c r="X11" s="31">
         <f>RAW!AA8</f>
-        <v>0</v>
-      </c>
-      <c r="X11" s="31">
-        <f>RAW!AB8</f>
         <v>100000</v>
       </c>
       <c r="Y11" s="31">
-        <f>RAW!AC8</f>
+        <f>RAW!AB8</f>
         <v>160000</v>
       </c>
-      <c r="Z11" s="31" t="e">
+      <c r="Z11" s="31">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>5710920</v>
       </c>
       <c r="AA11" s="37" t="str">
         <f t="shared" si="3"/>
@@ -85429,11 +85375,11 @@
         <v>18766000</v>
       </c>
       <c r="M12" s="29">
-        <f>RAW!P9</f>
+        <f>RAW!O9</f>
         <v>4266200</v>
       </c>
       <c r="N12" s="30">
-        <f>RAW!AD9</f>
+        <f>RAW!AC9</f>
         <v>0</v>
       </c>
       <c r="O12" s="31">
@@ -85441,43 +85387,43 @@
         <v>4266200</v>
       </c>
       <c r="P12" s="31">
-        <f>RAW!T9</f>
+        <f>RAW!S9</f>
         <v>27000</v>
       </c>
       <c r="Q12" s="31">
+        <f>RAW!T9</f>
+        <v>0</v>
+      </c>
+      <c r="R12" s="31">
         <f>RAW!U9</f>
         <v>0</v>
       </c>
-      <c r="R12" s="31">
+      <c r="S12" s="31">
         <f>RAW!V9</f>
         <v>0</v>
       </c>
-      <c r="S12" s="31">
+      <c r="T12" s="31">
         <f>RAW!W9</f>
         <v>0</v>
       </c>
-      <c r="T12" s="31">
+      <c r="U12" s="31">
         <f>RAW!X9</f>
         <v>0</v>
       </c>
-      <c r="U12" s="31">
+      <c r="V12" s="31">
         <f>RAW!Y9</f>
-        <v>0</v>
-      </c>
-      <c r="V12" s="31">
-        <f>RAW!Z9</f>
         <v>30000</v>
       </c>
       <c r="W12" s="31">
-        <f>RAW!AA9</f>
+        <f>RAW!Z9</f>
         <v>100000</v>
       </c>
       <c r="X12" s="31">
-        <f>RAW!AB9</f>
+        <f>RAW!AA9</f>
         <v>0</v>
       </c>
       <c r="Y12" s="31">
-        <f>RAW!AC9</f>
+        <f>RAW!AB9</f>
         <v>157000</v>
       </c>
       <c r="Z12" s="31">
@@ -85522,11 +85468,11 @@
         <v>17151250</v>
       </c>
       <c r="M13" s="29">
-        <f>RAW!P10</f>
+        <f>RAW!O10</f>
         <v>4154500</v>
       </c>
       <c r="N13" s="30">
-        <f>RAW!AD10</f>
+        <f>RAW!AC10</f>
         <v>0</v>
       </c>
       <c r="O13" s="31">
@@ -85534,43 +85480,43 @@
         <v>4154500</v>
       </c>
       <c r="P13" s="31">
-        <f>RAW!T10</f>
+        <f>RAW!S10</f>
         <v>120000</v>
       </c>
       <c r="Q13" s="31">
+        <f>RAW!T10</f>
+        <v>0</v>
+      </c>
+      <c r="R13" s="31">
         <f>RAW!U10</f>
         <v>0</v>
       </c>
-      <c r="R13" s="31">
+      <c r="S13" s="31">
         <f>RAW!V10</f>
         <v>0</v>
       </c>
-      <c r="S13" s="31">
+      <c r="T13" s="31">
         <f>RAW!W10</f>
         <v>0</v>
       </c>
-      <c r="T13" s="31">
+      <c r="U13" s="31">
         <f>RAW!X10</f>
         <v>0</v>
       </c>
-      <c r="U13" s="31">
+      <c r="V13" s="31">
         <f>RAW!Y10</f>
         <v>0</v>
       </c>
-      <c r="V13" s="31">
+      <c r="W13" s="31">
         <f>RAW!Z10</f>
         <v>0</v>
       </c>
-      <c r="W13" s="31">
+      <c r="X13" s="31">
         <f>RAW!AA10</f>
-        <v>0</v>
-      </c>
-      <c r="X13" s="31">
-        <f>RAW!AB10</f>
         <v>100000</v>
       </c>
       <c r="Y13" s="31">
-        <f>RAW!AC10</f>
+        <f>RAW!AB10</f>
         <v>220000</v>
       </c>
       <c r="Z13" s="31">
@@ -85615,11 +85561,11 @@
         <v>331000</v>
       </c>
       <c r="M14" s="29">
-        <f>RAW!P11</f>
+        <f>RAW!O11</f>
         <v>99300</v>
       </c>
       <c r="N14" s="30">
-        <f>RAW!AD11</f>
+        <f>RAW!AC11</f>
         <v>0</v>
       </c>
       <c r="O14" s="31">
@@ -85627,43 +85573,43 @@
         <v>99300</v>
       </c>
       <c r="P14" s="31">
-        <f>RAW!T11</f>
+        <f>RAW!S11</f>
         <v>52500</v>
       </c>
       <c r="Q14" s="31">
+        <f>RAW!T11</f>
+        <v>0</v>
+      </c>
+      <c r="R14" s="31">
         <f>RAW!U11</f>
         <v>0</v>
       </c>
-      <c r="R14" s="31">
+      <c r="S14" s="31">
         <f>RAW!V11</f>
         <v>0</v>
       </c>
-      <c r="S14" s="31">
+      <c r="T14" s="31">
         <f>RAW!W11</f>
         <v>0</v>
       </c>
-      <c r="T14" s="31">
+      <c r="U14" s="31">
         <f>RAW!X11</f>
         <v>0</v>
       </c>
-      <c r="U14" s="31">
+      <c r="V14" s="31">
         <f>RAW!Y11</f>
         <v>0</v>
       </c>
-      <c r="V14" s="31">
+      <c r="W14" s="31">
         <f>RAW!Z11</f>
         <v>0</v>
       </c>
-      <c r="W14" s="31">
+      <c r="X14" s="31">
         <f>RAW!AA11</f>
         <v>0</v>
       </c>
-      <c r="X14" s="31">
+      <c r="Y14" s="31">
         <f>RAW!AB11</f>
-        <v>0</v>
-      </c>
-      <c r="Y14" s="31">
-        <f>RAW!AC11</f>
         <v>52500</v>
       </c>
       <c r="Z14" s="31">
@@ -85708,11 +85654,11 @@
         <v>150000</v>
       </c>
       <c r="M15" s="29">
-        <f>RAW!P12</f>
+        <f>RAW!O12</f>
         <v>30000</v>
       </c>
       <c r="N15" s="30">
-        <f>RAW!AD12</f>
+        <f>RAW!AC12</f>
         <v>0</v>
       </c>
       <c r="O15" s="31">
@@ -85720,43 +85666,43 @@
         <v>30000</v>
       </c>
       <c r="P15" s="31">
+        <f>RAW!S12</f>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="31">
         <f>RAW!T12</f>
         <v>0</v>
       </c>
-      <c r="Q15" s="31">
+      <c r="R15" s="31">
         <f>RAW!U12</f>
         <v>0</v>
       </c>
-      <c r="R15" s="31">
+      <c r="S15" s="31">
         <f>RAW!V12</f>
         <v>0</v>
       </c>
-      <c r="S15" s="31">
+      <c r="T15" s="31">
         <f>RAW!W12</f>
         <v>0</v>
       </c>
-      <c r="T15" s="31">
+      <c r="U15" s="31">
         <f>RAW!X12</f>
         <v>0</v>
       </c>
-      <c r="U15" s="31">
+      <c r="V15" s="31">
         <f>RAW!Y12</f>
         <v>0</v>
       </c>
-      <c r="V15" s="31">
+      <c r="W15" s="31">
         <f>RAW!Z12</f>
         <v>0</v>
       </c>
-      <c r="W15" s="31">
+      <c r="X15" s="31">
         <f>RAW!AA12</f>
         <v>0</v>
       </c>
-      <c r="X15" s="31">
+      <c r="Y15" s="31">
         <f>RAW!AB12</f>
-        <v>0</v>
-      </c>
-      <c r="Y15" s="31">
-        <f>RAW!AC12</f>
         <v>0</v>
       </c>
       <c r="Z15" s="31">
@@ -85769,18 +85715,18 @@
       </c>
     </row>
     <row r="16" spans="2:34" s="5" customFormat="1" ht="69" customHeight="1">
-      <c r="B16" s="80" t="s">
+      <c r="B16" s="79" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="80"/>
-      <c r="D16" s="80"/>
-      <c r="E16" s="80"/>
-      <c r="F16" s="80"/>
-      <c r="G16" s="80"/>
-      <c r="H16" s="80"/>
-      <c r="I16" s="80"/>
-      <c r="J16" s="80"/>
-      <c r="K16" s="80"/>
+      <c r="C16" s="79"/>
+      <c r="D16" s="79"/>
+      <c r="E16" s="79"/>
+      <c r="F16" s="79"/>
+      <c r="G16" s="79"/>
+      <c r="H16" s="79"/>
+      <c r="I16" s="79"/>
+      <c r="J16" s="79"/>
+      <c r="K16" s="79"/>
       <c r="L16" s="32">
         <f>SUM(L8:L15)</f>
         <v>165572750</v>
@@ -85798,43 +85744,43 @@
         <v>8550000</v>
       </c>
       <c r="P16" s="32">
-        <f>SUM(P8:P15)</f>
+        <f t="shared" ref="P16:Y16" si="5">SUM(P8:P15)</f>
         <v>343800</v>
       </c>
       <c r="Q16" s="32">
-        <f>SUM(Q8:Q15)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R16" s="32">
-        <f>SUM(R8:R15)</f>
+        <f t="shared" si="5"/>
         <v>343805</v>
       </c>
       <c r="S16" s="32">
-        <f>SUM(S8:S15)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="T16" s="32">
-        <f>SUM(T8:T15)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="U16" s="32">
-        <f>SUM(U8:U15)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V16" s="32">
-        <f>SUM(V8:V15)</f>
+        <f t="shared" si="5"/>
         <v>30000</v>
       </c>
       <c r="W16" s="32">
-        <f>SUM(W8:W15)</f>
+        <f t="shared" si="5"/>
         <v>100000</v>
       </c>
       <c r="X16" s="32">
-        <f>SUM(X8:X15)</f>
+        <f t="shared" si="5"/>
         <v>500000</v>
       </c>
       <c r="Y16" s="32">
-        <f>SUM(Y8:Y15)</f>
+        <f t="shared" si="5"/>
         <v>1317605</v>
       </c>
       <c r="Z16" s="32">

--- a/final.xlsx
+++ b/final.xlsx
@@ -320,16 +320,15 @@
     <numFmt numFmtId="168" formatCode="0000000000000"/>
     <numFmt numFmtId="169" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="19">
     <font>
       <sz val="11.0"/>
-      <color/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11.0"/>
-      <color/>
       <name val="Calibri"/>
     </font>
     <font/>
@@ -385,23 +384,12 @@
       <name val="Cambria"/>
     </font>
     <font>
-      <b/>
-      <sz val="22.0"/>
-      <color/>
-      <name val="Cambria"/>
-    </font>
-    <font>
       <sz val="20.0"/>
       <name val="Cambria"/>
     </font>
     <font>
       <sz val="22.0"/>
       <color rgb="FF000000"/>
-      <name val="Cambria"/>
-    </font>
-    <font>
-      <sz val="22.0"/>
-      <color/>
       <name val="Cambria"/>
     </font>
     <font>
@@ -487,8 +475,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC2D69B"/>
-        <bgColor rgb="FFC2D69B"/>
+        <fgColor rgb="FFD9EAD3"/>
+        <bgColor rgb="FFD9EAD3"/>
       </patternFill>
     </fill>
     <fill>
@@ -595,7 +583,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="74">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
@@ -737,88 +725,85 @@
     <xf borderId="4" fillId="13" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="14" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="14" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="2" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
     <xf borderId="4" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="15" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="0" fontId="14" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="10" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="17" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="0" fontId="15" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="19" numFmtId="14" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="17" numFmtId="14" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="10" numFmtId="167" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="19" numFmtId="168" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="17" numFmtId="168" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="19" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="17" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="19" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="17" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="20" numFmtId="169" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="18" numFmtId="169" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="20" numFmtId="167" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="18" numFmtId="167" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="20" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="18" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1207,7 +1192,7 @@
     <col customWidth="1" min="3" max="3" width="8.71"/>
     <col customWidth="1" min="4" max="4" width="29.0"/>
     <col customWidth="1" min="5" max="5" width="20.29"/>
-    <col customWidth="1" min="6" max="11" width="8.71"/>
+    <col customWidth="1" min="6" max="6" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6053,11 +6038,11 @@
         <f>RAW!B5</f>
         <v>JATIMULYA</v>
       </c>
-      <c r="G8" s="53" t="s">
+      <c r="G8" s="50" t="s">
         <v>84</v>
       </c>
       <c r="H8" s="50"/>
-      <c r="I8" s="54"/>
+      <c r="I8" s="53"/>
       <c r="J8" s="50" t="str">
         <f t="shared" ref="J8:J15" si="1">CONCATENATE($G$7,G8,$H$7,H8,$I$7,I8)</f>
         <v>Bank BSI No. Rek.  A/n </v>
@@ -6065,67 +6050,67 @@
       <c r="K8" s="50" t="s">
         <v>85</v>
       </c>
-      <c r="L8" s="55" t="str">
+      <c r="L8" s="54" t="str">
         <f>RAW!I5</f>
         <v>  40,400,000 </v>
       </c>
-      <c r="M8" s="55" t="str">
+      <c r="M8" s="54" t="str">
         <f>RAW!O5</f>
         <v>  10,714,040 </v>
       </c>
-      <c r="N8" s="56" t="str">
+      <c r="N8" s="55" t="str">
         <f>RAW!AC5</f>
         <v>  - </v>
       </c>
-      <c r="O8" s="56" t="str">
+      <c r="O8" s="55" t="str">
         <f t="shared" ref="O8:O15" si="2">SUM(M8:N8)</f>
         <v>  10,714,040 </v>
       </c>
-      <c r="P8" s="56" t="str">
+      <c r="P8" s="55" t="str">
         <f>RAW!S5</f>
         <v/>
       </c>
-      <c r="Q8" s="56" t="str">
+      <c r="Q8" s="55" t="str">
         <f>RAW!T5</f>
         <v/>
       </c>
-      <c r="R8" s="56" t="str">
+      <c r="R8" s="55" t="str">
         <f>RAW!U5</f>
         <v/>
       </c>
-      <c r="S8" s="56" t="str">
+      <c r="S8" s="55" t="str">
         <f>RAW!V5</f>
         <v/>
       </c>
-      <c r="T8" s="56" t="str">
+      <c r="T8" s="55" t="str">
         <f>RAW!W5</f>
         <v/>
       </c>
-      <c r="U8" s="56" t="str">
+      <c r="U8" s="55" t="str">
         <f>RAW!X5</f>
         <v/>
       </c>
-      <c r="V8" s="56" t="str">
+      <c r="V8" s="55" t="str">
         <f>RAW!Y5</f>
         <v/>
       </c>
-      <c r="W8" s="56" t="str">
+      <c r="W8" s="55" t="str">
         <f>RAW!Z5</f>
         <v/>
       </c>
-      <c r="X8" s="56" t="str">
+      <c r="X8" s="55" t="str">
         <f>RAW!AA5</f>
         <v>  100,000 </v>
       </c>
-      <c r="Y8" s="56" t="str">
+      <c r="Y8" s="55" t="str">
         <f>RAW!AB5</f>
         <v>  100,000 </v>
       </c>
-      <c r="Z8" s="56" t="str">
+      <c r="Z8" s="55" t="str">
         <f t="shared" ref="Z8:Z15" si="3">O8-Y8</f>
         <v>  10,614,040 </v>
       </c>
-      <c r="AA8" s="57" t="str">
+      <c r="AA8" s="56" t="str">
         <f t="shared" ref="AA8:AA15" si="4">TEXTJOIN(" | ",TRUE,IF(V8&gt;0,"Biaya Pendaftaran Koperasi: "&amp;TEXT(V8,"#.##0"),""),IF(W8&gt;0,"Simpanan Pokok: "&amp;TEXT(W8,"#.##0"),""),IF(X8&gt;0,"Simpanan Wajib: "&amp;TEXT(X8,"#.##0"),""))</f>
         <v>Simpanan Wajib: 100000.0</v>
       </c>
@@ -6154,11 +6139,11 @@
         <f>RAW!B6</f>
         <v>JATIMULYA</v>
       </c>
-      <c r="G9" s="53" t="s">
+      <c r="G9" s="50" t="s">
         <v>84</v>
       </c>
       <c r="H9" s="50"/>
-      <c r="I9" s="54"/>
+      <c r="I9" s="53"/>
       <c r="J9" s="50" t="str">
         <f t="shared" si="1"/>
         <v>Bank BSI No. Rek.  A/n </v>
@@ -6166,67 +6151,67 @@
       <c r="K9" s="50" t="s">
         <v>85</v>
       </c>
-      <c r="L9" s="55" t="str">
+      <c r="L9" s="54" t="str">
         <f>RAW!I6</f>
         <v>  34,123,500 </v>
       </c>
-      <c r="M9" s="55" t="str">
+      <c r="M9" s="54" t="str">
         <f>RAW!O6</f>
         <v>  10,252,520 </v>
       </c>
-      <c r="N9" s="56" t="str">
+      <c r="N9" s="55" t="str">
         <f>RAW!AC6</f>
         <v>  - </v>
       </c>
-      <c r="O9" s="56" t="str">
+      <c r="O9" s="55" t="str">
         <f t="shared" si="2"/>
         <v>  10,252,520 </v>
       </c>
-      <c r="P9" s="56" t="str">
+      <c r="P9" s="55" t="str">
         <f>RAW!S6</f>
         <v/>
       </c>
-      <c r="Q9" s="56" t="str">
+      <c r="Q9" s="55" t="str">
         <f>RAW!T6</f>
         <v/>
       </c>
-      <c r="R9" s="56" t="str">
+      <c r="R9" s="55" t="str">
         <f>RAW!U6</f>
         <v>  343,805 </v>
       </c>
-      <c r="S9" s="56" t="str">
+      <c r="S9" s="55" t="str">
         <f>RAW!V6</f>
         <v/>
       </c>
-      <c r="T9" s="56" t="str">
+      <c r="T9" s="55" t="str">
         <f>RAW!W6</f>
         <v/>
       </c>
-      <c r="U9" s="56" t="str">
+      <c r="U9" s="55" t="str">
         <f>RAW!X6</f>
         <v/>
       </c>
-      <c r="V9" s="56" t="str">
+      <c r="V9" s="55" t="str">
         <f>RAW!Y6</f>
         <v/>
       </c>
-      <c r="W9" s="56" t="str">
+      <c r="W9" s="55" t="str">
         <f>RAW!Z6</f>
         <v/>
       </c>
-      <c r="X9" s="56" t="str">
+      <c r="X9" s="55" t="str">
         <f>RAW!AA6</f>
         <v>  100,000 </v>
       </c>
-      <c r="Y9" s="56" t="str">
+      <c r="Y9" s="55" t="str">
         <f>RAW!AB6</f>
         <v>  443,805 </v>
       </c>
-      <c r="Z9" s="56" t="str">
+      <c r="Z9" s="55" t="str">
         <f t="shared" si="3"/>
         <v>  9,808,715 </v>
       </c>
-      <c r="AA9" s="57" t="str">
+      <c r="AA9" s="56" t="str">
         <f t="shared" si="4"/>
         <v>Simpanan Wajib: 100000.0</v>
       </c>
@@ -6255,11 +6240,11 @@
         <f>RAW!B7</f>
         <v>JATIMULYA</v>
       </c>
-      <c r="G10" s="53" t="s">
+      <c r="G10" s="50" t="s">
         <v>84</v>
       </c>
       <c r="H10" s="50"/>
-      <c r="I10" s="54"/>
+      <c r="I10" s="53"/>
       <c r="J10" s="50" t="str">
         <f t="shared" si="1"/>
         <v>Bank BSI No. Rek.  A/n </v>
@@ -6267,67 +6252,67 @@
       <c r="K10" s="50" t="s">
         <v>85</v>
       </c>
-      <c r="L10" s="55" t="str">
+      <c r="L10" s="54" t="str">
         <f>RAW!I7</f>
         <v>  31,339,000 </v>
       </c>
-      <c r="M10" s="55" t="str">
+      <c r="M10" s="54" t="str">
         <f>RAW!O7</f>
         <v>  8,265,240 </v>
       </c>
-      <c r="N10" s="56" t="str">
+      <c r="N10" s="55" t="str">
         <f>RAW!AC7</f>
         <v>  - </v>
       </c>
-      <c r="O10" s="56" t="str">
+      <c r="O10" s="55" t="str">
         <f t="shared" si="2"/>
         <v>  8,265,240 </v>
       </c>
-      <c r="P10" s="56" t="str">
+      <c r="P10" s="55" t="str">
         <f>RAW!S7</f>
         <v>  84,300 </v>
       </c>
-      <c r="Q10" s="56" t="str">
+      <c r="Q10" s="55" t="str">
         <f>RAW!T7</f>
         <v/>
       </c>
-      <c r="R10" s="56" t="str">
+      <c r="R10" s="55" t="str">
         <f>RAW!U7</f>
         <v/>
       </c>
-      <c r="S10" s="56" t="str">
+      <c r="S10" s="55" t="str">
         <f>RAW!V7</f>
         <v/>
       </c>
-      <c r="T10" s="56" t="str">
+      <c r="T10" s="55" t="str">
         <f>RAW!W7</f>
         <v/>
       </c>
-      <c r="U10" s="56" t="str">
+      <c r="U10" s="55" t="str">
         <f>RAW!X7</f>
         <v/>
       </c>
-      <c r="V10" s="56" t="str">
+      <c r="V10" s="55" t="str">
         <f>RAW!Y7</f>
         <v/>
       </c>
-      <c r="W10" s="56" t="str">
+      <c r="W10" s="55" t="str">
         <f>RAW!Z7</f>
         <v/>
       </c>
-      <c r="X10" s="56" t="str">
+      <c r="X10" s="55" t="str">
         <f>RAW!AA7</f>
         <v>  100,000 </v>
       </c>
-      <c r="Y10" s="56" t="str">
+      <c r="Y10" s="55" t="str">
         <f>RAW!AB7</f>
         <v>  184,300 </v>
       </c>
-      <c r="Z10" s="56" t="str">
+      <c r="Z10" s="55" t="str">
         <f t="shared" si="3"/>
         <v>  8,080,940 </v>
       </c>
-      <c r="AA10" s="57" t="str">
+      <c r="AA10" s="56" t="str">
         <f t="shared" si="4"/>
         <v>Simpanan Wajib: 100000.0</v>
       </c>
@@ -6356,11 +6341,11 @@
         <f>RAW!B8</f>
         <v>JATIMULYA</v>
       </c>
-      <c r="G11" s="53" t="s">
+      <c r="G11" s="50" t="s">
         <v>84</v>
       </c>
       <c r="H11" s="50"/>
-      <c r="I11" s="54"/>
+      <c r="I11" s="53"/>
       <c r="J11" s="50" t="str">
         <f t="shared" si="1"/>
         <v>Bank BSI No. Rek.  A/n </v>
@@ -6368,67 +6353,67 @@
       <c r="K11" s="50" t="s">
         <v>85</v>
       </c>
-      <c r="L11" s="55" t="str">
+      <c r="L11" s="54" t="str">
         <f>RAW!I8</f>
         <v>  23,312,000 </v>
       </c>
-      <c r="M11" s="55" t="str">
+      <c r="M11" s="54" t="str">
         <f>RAW!O8</f>
         <v>  5,870,920 </v>
       </c>
-      <c r="N11" s="56" t="str">
+      <c r="N11" s="55" t="str">
         <f>RAW!AC8</f>
         <v>  - </v>
       </c>
-      <c r="O11" s="56" t="str">
+      <c r="O11" s="55" t="str">
         <f t="shared" si="2"/>
         <v>  5,870,920 </v>
       </c>
-      <c r="P11" s="56" t="str">
+      <c r="P11" s="55" t="str">
         <f>RAW!S8</f>
         <v>  60,000 </v>
       </c>
-      <c r="Q11" s="56" t="str">
+      <c r="Q11" s="55" t="str">
         <f>RAW!T8</f>
         <v/>
       </c>
-      <c r="R11" s="56" t="str">
+      <c r="R11" s="55" t="str">
         <f>RAW!U8</f>
         <v/>
       </c>
-      <c r="S11" s="56" t="str">
+      <c r="S11" s="55" t="str">
         <f>RAW!V8</f>
         <v/>
       </c>
-      <c r="T11" s="56" t="str">
+      <c r="T11" s="55" t="str">
         <f>RAW!W8</f>
         <v/>
       </c>
-      <c r="U11" s="56" t="str">
+      <c r="U11" s="55" t="str">
         <f>RAW!X8</f>
         <v/>
       </c>
-      <c r="V11" s="56" t="str">
+      <c r="V11" s="55" t="str">
         <f>RAW!Y8</f>
         <v/>
       </c>
-      <c r="W11" s="56" t="str">
+      <c r="W11" s="55" t="str">
         <f>RAW!Z8</f>
         <v/>
       </c>
-      <c r="X11" s="56" t="str">
+      <c r="X11" s="55" t="str">
         <f>RAW!AA8</f>
         <v>  100,000 </v>
       </c>
-      <c r="Y11" s="56" t="str">
+      <c r="Y11" s="55" t="str">
         <f>RAW!AB8</f>
         <v>  160,000 </v>
       </c>
-      <c r="Z11" s="56" t="str">
+      <c r="Z11" s="55" t="str">
         <f t="shared" si="3"/>
         <v>  5,710,920 </v>
       </c>
-      <c r="AA11" s="57" t="str">
+      <c r="AA11" s="56" t="str">
         <f t="shared" si="4"/>
         <v>Simpanan Wajib: 100000.0</v>
       </c>
@@ -6457,7 +6442,7 @@
         <f>RAW!B9</f>
         <v>JATIMULYA</v>
       </c>
-      <c r="G12" s="53" t="s">
+      <c r="G12" s="50" t="s">
         <v>84</v>
       </c>
       <c r="H12" s="50"/>
@@ -6469,67 +6454,67 @@
       <c r="K12" s="50" t="s">
         <v>85</v>
       </c>
-      <c r="L12" s="55" t="str">
+      <c r="L12" s="54" t="str">
         <f>RAW!I9</f>
         <v>  18,766,000 </v>
       </c>
-      <c r="M12" s="55" t="str">
+      <c r="M12" s="54" t="str">
         <f>RAW!O9</f>
         <v>  4,266,200 </v>
       </c>
-      <c r="N12" s="56" t="str">
+      <c r="N12" s="55" t="str">
         <f>RAW!AC9</f>
         <v>  - </v>
       </c>
-      <c r="O12" s="56" t="str">
+      <c r="O12" s="55" t="str">
         <f t="shared" si="2"/>
         <v>  4,266,200 </v>
       </c>
-      <c r="P12" s="56" t="str">
+      <c r="P12" s="55" t="str">
         <f>RAW!S9</f>
         <v>  27,000 </v>
       </c>
-      <c r="Q12" s="56" t="str">
+      <c r="Q12" s="55" t="str">
         <f>RAW!T9</f>
         <v/>
       </c>
-      <c r="R12" s="56" t="str">
+      <c r="R12" s="55" t="str">
         <f>RAW!U9</f>
         <v/>
       </c>
-      <c r="S12" s="56" t="str">
+      <c r="S12" s="55" t="str">
         <f>RAW!V9</f>
         <v/>
       </c>
-      <c r="T12" s="56" t="str">
+      <c r="T12" s="55" t="str">
         <f>RAW!W9</f>
         <v/>
       </c>
-      <c r="U12" s="56" t="str">
+      <c r="U12" s="55" t="str">
         <f>RAW!X9</f>
         <v/>
       </c>
-      <c r="V12" s="56" t="str">
+      <c r="V12" s="55" t="str">
         <f>RAW!Y9</f>
         <v>  30,000 </v>
       </c>
-      <c r="W12" s="56" t="str">
+      <c r="W12" s="55" t="str">
         <f>RAW!Z9</f>
         <v>  100,000 </v>
       </c>
-      <c r="X12" s="56" t="str">
+      <c r="X12" s="55" t="str">
         <f>RAW!AA9</f>
         <v/>
       </c>
-      <c r="Y12" s="56" t="str">
+      <c r="Y12" s="55" t="str">
         <f>RAW!AB9</f>
         <v>  157,000 </v>
       </c>
-      <c r="Z12" s="56" t="str">
+      <c r="Z12" s="55" t="str">
         <f t="shared" si="3"/>
         <v>  4,109,200 </v>
       </c>
-      <c r="AA12" s="57" t="str">
+      <c r="AA12" s="56" t="str">
         <f t="shared" si="4"/>
         <v>Biaya Pendaftaran Koperasi: 30000.0 | Simpanan Pokok: 100000.0</v>
       </c>
@@ -6558,11 +6543,11 @@
         <f>RAW!B10</f>
         <v>JATIMULYA</v>
       </c>
-      <c r="G13" s="53" t="s">
+      <c r="G13" s="50" t="s">
         <v>84</v>
       </c>
       <c r="H13" s="50"/>
-      <c r="I13" s="54"/>
+      <c r="I13" s="53"/>
       <c r="J13" s="50" t="str">
         <f t="shared" si="1"/>
         <v>Bank BSI No. Rek.  A/n </v>
@@ -6570,67 +6555,67 @@
       <c r="K13" s="50" t="s">
         <v>85</v>
       </c>
-      <c r="L13" s="55" t="str">
+      <c r="L13" s="54" t="str">
         <f>RAW!I10</f>
         <v>  17,151,250 </v>
       </c>
-      <c r="M13" s="55" t="str">
+      <c r="M13" s="54" t="str">
         <f>RAW!O10</f>
         <v>  4,154,500 </v>
       </c>
-      <c r="N13" s="56" t="str">
+      <c r="N13" s="55" t="str">
         <f>RAW!AC10</f>
         <v>  - </v>
       </c>
-      <c r="O13" s="56" t="str">
+      <c r="O13" s="55" t="str">
         <f t="shared" si="2"/>
         <v>  4,154,500 </v>
       </c>
-      <c r="P13" s="56" t="str">
+      <c r="P13" s="55" t="str">
         <f>RAW!S10</f>
         <v>  120,000 </v>
       </c>
-      <c r="Q13" s="56" t="str">
+      <c r="Q13" s="55" t="str">
         <f>RAW!T10</f>
         <v/>
       </c>
-      <c r="R13" s="56" t="str">
+      <c r="R13" s="55" t="str">
         <f>RAW!U10</f>
         <v/>
       </c>
-      <c r="S13" s="56" t="str">
+      <c r="S13" s="55" t="str">
         <f>RAW!V10</f>
         <v/>
       </c>
-      <c r="T13" s="56" t="str">
+      <c r="T13" s="55" t="str">
         <f>RAW!W10</f>
         <v/>
       </c>
-      <c r="U13" s="56" t="str">
+      <c r="U13" s="55" t="str">
         <f>RAW!X10</f>
         <v/>
       </c>
-      <c r="V13" s="56" t="str">
+      <c r="V13" s="55" t="str">
         <f>RAW!Y10</f>
         <v/>
       </c>
-      <c r="W13" s="56" t="str">
+      <c r="W13" s="55" t="str">
         <f>RAW!Z10</f>
         <v/>
       </c>
-      <c r="X13" s="56" t="str">
+      <c r="X13" s="55" t="str">
         <f>RAW!AA10</f>
         <v>  100,000 </v>
       </c>
-      <c r="Y13" s="56" t="str">
+      <c r="Y13" s="55" t="str">
         <f>RAW!AB10</f>
         <v>  220,000 </v>
       </c>
-      <c r="Z13" s="56" t="str">
+      <c r="Z13" s="55" t="str">
         <f t="shared" si="3"/>
         <v>  3,934,500 </v>
       </c>
-      <c r="AA13" s="57" t="str">
+      <c r="AA13" s="56" t="str">
         <f t="shared" si="4"/>
         <v>Simpanan Wajib: 100000.0</v>
       </c>
@@ -6659,11 +6644,11 @@
         <f>RAW!B11</f>
         <v>JATIMULYA</v>
       </c>
-      <c r="G14" s="53" t="s">
+      <c r="G14" s="50" t="s">
         <v>84</v>
       </c>
       <c r="H14" s="50"/>
-      <c r="I14" s="54"/>
+      <c r="I14" s="53"/>
       <c r="J14" s="50" t="str">
         <f t="shared" si="1"/>
         <v>Bank BSI No. Rek.  A/n </v>
@@ -6671,67 +6656,67 @@
       <c r="K14" s="50" t="s">
         <v>85</v>
       </c>
-      <c r="L14" s="55" t="str">
+      <c r="L14" s="54" t="str">
         <f>RAW!I11</f>
         <v>  331,000 </v>
       </c>
-      <c r="M14" s="55" t="str">
+      <c r="M14" s="54" t="str">
         <f>RAW!O11</f>
         <v>  99,300 </v>
       </c>
-      <c r="N14" s="56" t="str">
+      <c r="N14" s="55" t="str">
         <f>RAW!AC11</f>
         <v>  - </v>
       </c>
-      <c r="O14" s="56" t="str">
+      <c r="O14" s="55" t="str">
         <f t="shared" si="2"/>
         <v>  99,300 </v>
       </c>
-      <c r="P14" s="56" t="str">
+      <c r="P14" s="55" t="str">
         <f>RAW!S11</f>
         <v>  52,500 </v>
       </c>
-      <c r="Q14" s="56" t="str">
+      <c r="Q14" s="55" t="str">
         <f>RAW!T11</f>
         <v/>
       </c>
-      <c r="R14" s="56" t="str">
+      <c r="R14" s="55" t="str">
         <f>RAW!U11</f>
         <v/>
       </c>
-      <c r="S14" s="56" t="str">
+      <c r="S14" s="55" t="str">
         <f>RAW!V11</f>
         <v/>
       </c>
-      <c r="T14" s="56" t="str">
+      <c r="T14" s="55" t="str">
         <f>RAW!W11</f>
         <v/>
       </c>
-      <c r="U14" s="56" t="str">
+      <c r="U14" s="55" t="str">
         <f>RAW!X11</f>
         <v/>
       </c>
-      <c r="V14" s="56" t="str">
+      <c r="V14" s="55" t="str">
         <f>RAW!Y11</f>
         <v/>
       </c>
-      <c r="W14" s="56" t="str">
+      <c r="W14" s="55" t="str">
         <f>RAW!Z11</f>
         <v/>
       </c>
-      <c r="X14" s="56" t="str">
+      <c r="X14" s="55" t="str">
         <f>RAW!AA11</f>
         <v/>
       </c>
-      <c r="Y14" s="56" t="str">
+      <c r="Y14" s="55" t="str">
         <f>RAW!AB11</f>
         <v>  52,500 </v>
       </c>
-      <c r="Z14" s="56" t="str">
+      <c r="Z14" s="55" t="str">
         <f t="shared" si="3"/>
         <v>  46,800 </v>
       </c>
-      <c r="AA14" s="57" t="str">
+      <c r="AA14" s="56" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -6760,7 +6745,7 @@
         <f>RAW!B12</f>
         <v>JATIMULYA</v>
       </c>
-      <c r="G15" s="53" t="s">
+      <c r="G15" s="50" t="s">
         <v>84</v>
       </c>
       <c r="H15" s="50"/>
@@ -6772,67 +6757,67 @@
       <c r="K15" s="50" t="s">
         <v>85</v>
       </c>
-      <c r="L15" s="55" t="str">
+      <c r="L15" s="54" t="str">
         <f>RAW!I12</f>
         <v>  150,000 </v>
       </c>
-      <c r="M15" s="55" t="str">
+      <c r="M15" s="54" t="str">
         <f>RAW!O12</f>
         <v>  30,000 </v>
       </c>
-      <c r="N15" s="56" t="str">
+      <c r="N15" s="55" t="str">
         <f>RAW!AC12</f>
         <v>  - </v>
       </c>
-      <c r="O15" s="56" t="str">
+      <c r="O15" s="55" t="str">
         <f t="shared" si="2"/>
         <v>  30,000 </v>
       </c>
-      <c r="P15" s="56" t="str">
+      <c r="P15" s="55" t="str">
         <f>RAW!S12</f>
         <v/>
       </c>
-      <c r="Q15" s="56" t="str">
+      <c r="Q15" s="55" t="str">
         <f>RAW!T12</f>
         <v/>
       </c>
-      <c r="R15" s="56" t="str">
+      <c r="R15" s="55" t="str">
         <f>RAW!U12</f>
         <v/>
       </c>
-      <c r="S15" s="56" t="str">
+      <c r="S15" s="55" t="str">
         <f>RAW!V12</f>
         <v/>
       </c>
-      <c r="T15" s="56" t="str">
+      <c r="T15" s="55" t="str">
         <f>RAW!W12</f>
         <v/>
       </c>
-      <c r="U15" s="56" t="str">
+      <c r="U15" s="55" t="str">
         <f>RAW!X12</f>
         <v/>
       </c>
-      <c r="V15" s="56" t="str">
+      <c r="V15" s="55" t="str">
         <f>RAW!Y12</f>
         <v/>
       </c>
-      <c r="W15" s="56" t="str">
+      <c r="W15" s="55" t="str">
         <f>RAW!Z12</f>
         <v/>
       </c>
-      <c r="X15" s="56" t="str">
+      <c r="X15" s="55" t="str">
         <f>RAW!AA12</f>
         <v/>
       </c>
-      <c r="Y15" s="56" t="str">
+      <c r="Y15" s="55" t="str">
         <f>RAW!AB12</f>
         <v>  - </v>
       </c>
-      <c r="Z15" s="56" t="str">
+      <c r="Z15" s="55" t="str">
         <f t="shared" si="3"/>
         <v>  30,000 </v>
       </c>
-      <c r="AA15" s="57" t="str">
+      <c r="AA15" s="56" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -6845,8 +6830,8 @@
       <c r="AH15" s="49"/>
     </row>
     <row r="16" ht="69.0" customHeight="1">
-      <c r="A16" s="58"/>
-      <c r="B16" s="59" t="s">
+      <c r="A16" s="57"/>
+      <c r="B16" s="58" t="s">
         <v>62</v>
       </c>
       <c r="C16" s="2"/>
@@ -6858,74 +6843,74 @@
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="3"/>
-      <c r="L16" s="60" t="str">
+      <c r="L16" s="59" t="str">
         <f t="shared" ref="L16:Z16" si="5">SUM(L8:L15)</f>
         <v> Rp 165,572,750 </v>
       </c>
-      <c r="M16" s="60" t="str">
+      <c r="M16" s="59" t="str">
         <f t="shared" si="5"/>
         <v> Rp 43,652,720 </v>
       </c>
-      <c r="N16" s="60" t="str">
+      <c r="N16" s="59" t="str">
         <f t="shared" si="5"/>
         <v> Rp - </v>
       </c>
-      <c r="O16" s="60" t="str">
+      <c r="O16" s="59" t="str">
         <f t="shared" si="5"/>
         <v> Rp 43,652,720 </v>
       </c>
-      <c r="P16" s="60" t="str">
+      <c r="P16" s="59" t="str">
         <f t="shared" si="5"/>
         <v> Rp 343,800 </v>
       </c>
-      <c r="Q16" s="60" t="str">
+      <c r="Q16" s="59" t="str">
         <f t="shared" si="5"/>
         <v> Rp - </v>
       </c>
-      <c r="R16" s="60" t="str">
+      <c r="R16" s="59" t="str">
         <f t="shared" si="5"/>
         <v> Rp 343,805 </v>
       </c>
-      <c r="S16" s="60" t="str">
+      <c r="S16" s="59" t="str">
         <f t="shared" si="5"/>
         <v> Rp - </v>
       </c>
-      <c r="T16" s="60" t="str">
+      <c r="T16" s="59" t="str">
         <f t="shared" si="5"/>
         <v> Rp - </v>
       </c>
-      <c r="U16" s="60" t="str">
+      <c r="U16" s="59" t="str">
         <f t="shared" si="5"/>
         <v> Rp - </v>
       </c>
-      <c r="V16" s="60" t="str">
+      <c r="V16" s="59" t="str">
         <f t="shared" si="5"/>
         <v> Rp 30,000 </v>
       </c>
-      <c r="W16" s="60" t="str">
+      <c r="W16" s="59" t="str">
         <f t="shared" si="5"/>
         <v> Rp 100,000 </v>
       </c>
-      <c r="X16" s="60" t="str">
+      <c r="X16" s="59" t="str">
         <f t="shared" si="5"/>
         <v> Rp 500,000 </v>
       </c>
-      <c r="Y16" s="60" t="str">
+      <c r="Y16" s="59" t="str">
         <f t="shared" si="5"/>
         <v> Rp 1,317,605 </v>
       </c>
-      <c r="Z16" s="60" t="str">
+      <c r="Z16" s="59" t="str">
         <f t="shared" si="5"/>
         <v> Rp 42,335,115 </v>
       </c>
-      <c r="AA16" s="61"/>
-      <c r="AB16" s="58"/>
-      <c r="AC16" s="58"/>
-      <c r="AD16" s="58"/>
-      <c r="AE16" s="58"/>
-      <c r="AF16" s="58"/>
-      <c r="AG16" s="58"/>
-      <c r="AH16" s="58"/>
+      <c r="AA16" s="60"/>
+      <c r="AB16" s="57"/>
+      <c r="AC16" s="57"/>
+      <c r="AD16" s="57"/>
+      <c r="AE16" s="57"/>
+      <c r="AF16" s="57"/>
+      <c r="AG16" s="57"/>
+      <c r="AH16" s="57"/>
     </row>
     <row r="17" ht="25.5" customHeight="1">
       <c r="A17" s="30"/>
@@ -6954,7 +6939,7 @@
       <c r="X17" s="39"/>
       <c r="Y17" s="39"/>
       <c r="Z17" s="39"/>
-      <c r="AA17" s="62"/>
+      <c r="AA17" s="61"/>
       <c r="AB17" s="30"/>
       <c r="AC17" s="30"/>
       <c r="AD17" s="30"/>
@@ -7014,23 +6999,23 @@
       <c r="L19" s="30"/>
       <c r="M19" s="30"/>
       <c r="N19" s="30"/>
-      <c r="O19" s="63" t="s">
+      <c r="O19" s="62" t="s">
         <v>86</v>
       </c>
-      <c r="P19" s="64" t="str">
+      <c r="P19" s="63" t="str">
         <f>TODAY()</f>
         <v>8/27/2026</v>
       </c>
-      <c r="Q19" s="64"/>
-      <c r="R19" s="64"/>
-      <c r="S19" s="64"/>
-      <c r="T19" s="64"/>
-      <c r="U19" s="64"/>
-      <c r="V19" s="64"/>
-      <c r="W19" s="64"/>
-      <c r="X19" s="64"/>
+      <c r="Q19" s="63"/>
+      <c r="R19" s="63"/>
+      <c r="S19" s="63"/>
+      <c r="T19" s="63"/>
+      <c r="U19" s="63"/>
+      <c r="V19" s="63"/>
+      <c r="W19" s="63"/>
+      <c r="X19" s="63"/>
       <c r="Y19" s="30"/>
-      <c r="Z19" s="65"/>
+      <c r="Z19" s="64"/>
       <c r="AA19" s="30"/>
       <c r="AB19" s="30"/>
       <c r="AC19" s="30"/>
@@ -7041,352 +7026,352 @@
       <c r="AH19" s="30"/>
     </row>
     <row r="20" ht="57.75" customHeight="1">
-      <c r="A20" s="66"/>
-      <c r="B20" s="66"/>
-      <c r="C20" s="67"/>
-      <c r="D20" s="68" t="s">
+      <c r="A20" s="65"/>
+      <c r="B20" s="65"/>
+      <c r="C20" s="66"/>
+      <c r="D20" s="67" t="s">
         <v>87</v>
       </c>
-      <c r="E20" s="66"/>
-      <c r="F20" s="68"/>
-      <c r="G20" s="68"/>
-      <c r="H20" s="68"/>
-      <c r="I20" s="68"/>
-      <c r="J20" s="68"/>
-      <c r="K20" s="66"/>
-      <c r="L20" s="68"/>
-      <c r="M20" s="68"/>
-      <c r="N20" s="66"/>
-      <c r="O20" s="68" t="s">
+      <c r="E20" s="65"/>
+      <c r="F20" s="67"/>
+      <c r="G20" s="67"/>
+      <c r="H20" s="67"/>
+      <c r="I20" s="67"/>
+      <c r="J20" s="67"/>
+      <c r="K20" s="65"/>
+      <c r="L20" s="67"/>
+      <c r="M20" s="67"/>
+      <c r="N20" s="65"/>
+      <c r="O20" s="67" t="s">
         <v>88</v>
       </c>
-      <c r="P20" s="66"/>
-      <c r="Q20" s="66"/>
-      <c r="R20" s="66"/>
-      <c r="S20" s="68" t="s">
+      <c r="P20" s="65"/>
+      <c r="Q20" s="65"/>
+      <c r="R20" s="65"/>
+      <c r="S20" s="67" t="s">
         <v>88</v>
       </c>
-      <c r="T20" s="68"/>
-      <c r="U20" s="68"/>
-      <c r="V20" s="68"/>
-      <c r="W20" s="68"/>
-      <c r="X20" s="68"/>
-      <c r="Y20" s="68" t="s">
+      <c r="T20" s="67"/>
+      <c r="U20" s="67"/>
+      <c r="V20" s="67"/>
+      <c r="W20" s="67"/>
+      <c r="X20" s="67"/>
+      <c r="Y20" s="67" t="s">
         <v>88</v>
       </c>
-      <c r="Z20" s="69"/>
-      <c r="AA20" s="70"/>
-      <c r="AB20" s="66"/>
-      <c r="AC20" s="68"/>
-      <c r="AD20" s="68"/>
-      <c r="AE20" s="70"/>
-      <c r="AF20" s="70"/>
-      <c r="AG20" s="66"/>
-      <c r="AH20" s="66"/>
+      <c r="Z20" s="68"/>
+      <c r="AA20" s="69"/>
+      <c r="AB20" s="65"/>
+      <c r="AC20" s="67"/>
+      <c r="AD20" s="67"/>
+      <c r="AE20" s="69"/>
+      <c r="AF20" s="69"/>
+      <c r="AG20" s="65"/>
+      <c r="AH20" s="65"/>
     </row>
     <row r="21" ht="14.25" customHeight="1">
-      <c r="A21" s="66"/>
-      <c r="B21" s="66"/>
-      <c r="C21" s="67"/>
-      <c r="D21" s="68"/>
-      <c r="E21" s="66"/>
-      <c r="F21" s="68"/>
-      <c r="G21" s="68"/>
-      <c r="H21" s="68"/>
-      <c r="I21" s="68"/>
-      <c r="J21" s="68"/>
-      <c r="K21" s="66"/>
-      <c r="L21" s="68"/>
-      <c r="M21" s="68"/>
-      <c r="N21" s="66"/>
-      <c r="O21" s="68"/>
-      <c r="P21" s="68"/>
-      <c r="Q21" s="68"/>
-      <c r="R21" s="68"/>
-      <c r="S21" s="68"/>
-      <c r="T21" s="68"/>
-      <c r="U21" s="68"/>
-      <c r="V21" s="68"/>
-      <c r="W21" s="68"/>
-      <c r="X21" s="68"/>
-      <c r="Y21" s="68"/>
-      <c r="Z21" s="69"/>
-      <c r="AA21" s="70"/>
-      <c r="AB21" s="68"/>
-      <c r="AC21" s="68"/>
-      <c r="AD21" s="68"/>
-      <c r="AE21" s="70"/>
-      <c r="AF21" s="70"/>
-      <c r="AG21" s="66"/>
-      <c r="AH21" s="66"/>
+      <c r="A21" s="65"/>
+      <c r="B21" s="65"/>
+      <c r="C21" s="66"/>
+      <c r="D21" s="67"/>
+      <c r="E21" s="65"/>
+      <c r="F21" s="67"/>
+      <c r="G21" s="67"/>
+      <c r="H21" s="67"/>
+      <c r="I21" s="67"/>
+      <c r="J21" s="67"/>
+      <c r="K21" s="65"/>
+      <c r="L21" s="67"/>
+      <c r="M21" s="67"/>
+      <c r="N21" s="65"/>
+      <c r="O21" s="67"/>
+      <c r="P21" s="67"/>
+      <c r="Q21" s="67"/>
+      <c r="R21" s="67"/>
+      <c r="S21" s="67"/>
+      <c r="T21" s="67"/>
+      <c r="U21" s="67"/>
+      <c r="V21" s="67"/>
+      <c r="W21" s="67"/>
+      <c r="X21" s="67"/>
+      <c r="Y21" s="67"/>
+      <c r="Z21" s="68"/>
+      <c r="AA21" s="69"/>
+      <c r="AB21" s="67"/>
+      <c r="AC21" s="67"/>
+      <c r="AD21" s="67"/>
+      <c r="AE21" s="69"/>
+      <c r="AF21" s="69"/>
+      <c r="AG21" s="65"/>
+      <c r="AH21" s="65"/>
     </row>
     <row r="22" ht="14.25" customHeight="1">
-      <c r="A22" s="66"/>
-      <c r="B22" s="66"/>
-      <c r="C22" s="67"/>
-      <c r="D22" s="71"/>
-      <c r="E22" s="66"/>
-      <c r="F22" s="66"/>
-      <c r="G22" s="66"/>
-      <c r="H22" s="66"/>
-      <c r="I22" s="66"/>
-      <c r="J22" s="66"/>
-      <c r="K22" s="66"/>
-      <c r="L22" s="66"/>
-      <c r="M22" s="66"/>
-      <c r="N22" s="66"/>
-      <c r="O22" s="66"/>
-      <c r="P22" s="66"/>
-      <c r="Q22" s="66"/>
-      <c r="R22" s="66"/>
-      <c r="S22" s="66"/>
-      <c r="T22" s="66"/>
-      <c r="U22" s="66"/>
-      <c r="V22" s="66"/>
-      <c r="W22" s="66"/>
-      <c r="X22" s="66"/>
-      <c r="Y22" s="66"/>
-      <c r="Z22" s="72"/>
-      <c r="AA22" s="70"/>
-      <c r="AB22" s="66"/>
-      <c r="AC22" s="66"/>
-      <c r="AD22" s="66"/>
-      <c r="AE22" s="70"/>
-      <c r="AF22" s="70"/>
-      <c r="AG22" s="66"/>
-      <c r="AH22" s="66"/>
+      <c r="A22" s="65"/>
+      <c r="B22" s="65"/>
+      <c r="C22" s="66"/>
+      <c r="D22" s="70"/>
+      <c r="E22" s="65"/>
+      <c r="F22" s="65"/>
+      <c r="G22" s="65"/>
+      <c r="H22" s="65"/>
+      <c r="I22" s="65"/>
+      <c r="J22" s="65"/>
+      <c r="K22" s="65"/>
+      <c r="L22" s="65"/>
+      <c r="M22" s="65"/>
+      <c r="N22" s="65"/>
+      <c r="O22" s="65"/>
+      <c r="P22" s="65"/>
+      <c r="Q22" s="65"/>
+      <c r="R22" s="65"/>
+      <c r="S22" s="65"/>
+      <c r="T22" s="65"/>
+      <c r="U22" s="65"/>
+      <c r="V22" s="65"/>
+      <c r="W22" s="65"/>
+      <c r="X22" s="65"/>
+      <c r="Y22" s="65"/>
+      <c r="Z22" s="71"/>
+      <c r="AA22" s="69"/>
+      <c r="AB22" s="65"/>
+      <c r="AC22" s="65"/>
+      <c r="AD22" s="65"/>
+      <c r="AE22" s="69"/>
+      <c r="AF22" s="69"/>
+      <c r="AG22" s="65"/>
+      <c r="AH22" s="65"/>
     </row>
     <row r="23" ht="14.25" customHeight="1">
-      <c r="A23" s="66"/>
-      <c r="B23" s="66"/>
-      <c r="C23" s="67"/>
-      <c r="D23" s="71"/>
-      <c r="E23" s="66"/>
-      <c r="F23" s="66"/>
-      <c r="G23" s="66"/>
-      <c r="H23" s="66"/>
-      <c r="I23" s="66"/>
-      <c r="J23" s="66"/>
-      <c r="K23" s="66"/>
-      <c r="L23" s="66"/>
-      <c r="M23" s="66"/>
-      <c r="N23" s="66"/>
-      <c r="O23" s="66"/>
-      <c r="P23" s="73"/>
-      <c r="Q23" s="73"/>
-      <c r="R23" s="73"/>
-      <c r="S23" s="66"/>
-      <c r="T23" s="66"/>
-      <c r="U23" s="66"/>
-      <c r="V23" s="66"/>
-      <c r="W23" s="66"/>
-      <c r="X23" s="66"/>
-      <c r="Y23" s="66"/>
-      <c r="Z23" s="74"/>
-      <c r="AA23" s="70"/>
-      <c r="AB23" s="66"/>
-      <c r="AC23" s="66"/>
-      <c r="AD23" s="66"/>
-      <c r="AE23" s="70"/>
-      <c r="AF23" s="70"/>
-      <c r="AG23" s="66"/>
-      <c r="AH23" s="66"/>
+      <c r="A23" s="65"/>
+      <c r="B23" s="65"/>
+      <c r="C23" s="66"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="65"/>
+      <c r="F23" s="65"/>
+      <c r="G23" s="65"/>
+      <c r="H23" s="65"/>
+      <c r="I23" s="65"/>
+      <c r="J23" s="65"/>
+      <c r="K23" s="65"/>
+      <c r="L23" s="65"/>
+      <c r="M23" s="65"/>
+      <c r="N23" s="65"/>
+      <c r="O23" s="65"/>
+      <c r="P23" s="72"/>
+      <c r="Q23" s="72"/>
+      <c r="R23" s="72"/>
+      <c r="S23" s="65"/>
+      <c r="T23" s="65"/>
+      <c r="U23" s="65"/>
+      <c r="V23" s="65"/>
+      <c r="W23" s="65"/>
+      <c r="X23" s="65"/>
+      <c r="Y23" s="65"/>
+      <c r="Z23" s="73"/>
+      <c r="AA23" s="69"/>
+      <c r="AB23" s="65"/>
+      <c r="AC23" s="65"/>
+      <c r="AD23" s="65"/>
+      <c r="AE23" s="69"/>
+      <c r="AF23" s="69"/>
+      <c r="AG23" s="65"/>
+      <c r="AH23" s="65"/>
     </row>
     <row r="24" ht="14.25" customHeight="1">
-      <c r="A24" s="66"/>
-      <c r="B24" s="66"/>
-      <c r="C24" s="67"/>
-      <c r="D24" s="71"/>
-      <c r="E24" s="66"/>
-      <c r="F24" s="66"/>
-      <c r="G24" s="66"/>
-      <c r="H24" s="66"/>
-      <c r="I24" s="66"/>
-      <c r="J24" s="66"/>
-      <c r="K24" s="66"/>
-      <c r="L24" s="66"/>
-      <c r="M24" s="66"/>
-      <c r="N24" s="66"/>
-      <c r="O24" s="66"/>
-      <c r="P24" s="66"/>
-      <c r="Q24" s="66"/>
-      <c r="R24" s="66"/>
-      <c r="S24" s="66"/>
-      <c r="T24" s="66"/>
-      <c r="U24" s="66"/>
-      <c r="V24" s="66"/>
-      <c r="W24" s="66"/>
-      <c r="X24" s="66"/>
-      <c r="Y24" s="66"/>
-      <c r="Z24" s="66"/>
-      <c r="AA24" s="70"/>
-      <c r="AB24" s="66"/>
-      <c r="AC24" s="66"/>
-      <c r="AD24" s="66"/>
-      <c r="AE24" s="70"/>
-      <c r="AF24" s="70"/>
-      <c r="AG24" s="66"/>
-      <c r="AH24" s="66"/>
+      <c r="A24" s="65"/>
+      <c r="B24" s="65"/>
+      <c r="C24" s="66"/>
+      <c r="D24" s="70"/>
+      <c r="E24" s="65"/>
+      <c r="F24" s="65"/>
+      <c r="G24" s="65"/>
+      <c r="H24" s="65"/>
+      <c r="I24" s="65"/>
+      <c r="J24" s="65"/>
+      <c r="K24" s="65"/>
+      <c r="L24" s="65"/>
+      <c r="M24" s="65"/>
+      <c r="N24" s="65"/>
+      <c r="O24" s="65"/>
+      <c r="P24" s="65"/>
+      <c r="Q24" s="65"/>
+      <c r="R24" s="65"/>
+      <c r="S24" s="65"/>
+      <c r="T24" s="65"/>
+      <c r="U24" s="65"/>
+      <c r="V24" s="65"/>
+      <c r="W24" s="65"/>
+      <c r="X24" s="65"/>
+      <c r="Y24" s="65"/>
+      <c r="Z24" s="65"/>
+      <c r="AA24" s="69"/>
+      <c r="AB24" s="65"/>
+      <c r="AC24" s="65"/>
+      <c r="AD24" s="65"/>
+      <c r="AE24" s="69"/>
+      <c r="AF24" s="69"/>
+      <c r="AG24" s="65"/>
+      <c r="AH24" s="65"/>
     </row>
     <row r="25" ht="14.25" customHeight="1">
-      <c r="A25" s="66"/>
-      <c r="B25" s="66"/>
-      <c r="C25" s="67"/>
-      <c r="D25" s="68"/>
-      <c r="E25" s="66"/>
-      <c r="F25" s="66"/>
-      <c r="G25" s="66"/>
-      <c r="H25" s="66"/>
-      <c r="I25" s="66"/>
-      <c r="J25" s="66"/>
-      <c r="K25" s="66"/>
-      <c r="L25" s="66"/>
-      <c r="M25" s="66"/>
-      <c r="N25" s="66"/>
-      <c r="O25" s="66"/>
-      <c r="P25" s="66"/>
-      <c r="Q25" s="66"/>
-      <c r="R25" s="66"/>
-      <c r="S25" s="66"/>
-      <c r="T25" s="66"/>
-      <c r="U25" s="66"/>
-      <c r="V25" s="66"/>
-      <c r="W25" s="66"/>
-      <c r="X25" s="66"/>
-      <c r="Y25" s="66"/>
-      <c r="Z25" s="74"/>
-      <c r="AA25" s="66"/>
-      <c r="AB25" s="66"/>
-      <c r="AC25" s="66"/>
-      <c r="AD25" s="66"/>
-      <c r="AE25" s="66"/>
-      <c r="AF25" s="66"/>
-      <c r="AG25" s="66"/>
-      <c r="AH25" s="66"/>
+      <c r="A25" s="65"/>
+      <c r="B25" s="65"/>
+      <c r="C25" s="66"/>
+      <c r="D25" s="67"/>
+      <c r="E25" s="65"/>
+      <c r="F25" s="65"/>
+      <c r="G25" s="65"/>
+      <c r="H25" s="65"/>
+      <c r="I25" s="65"/>
+      <c r="J25" s="65"/>
+      <c r="K25" s="65"/>
+      <c r="L25" s="65"/>
+      <c r="M25" s="65"/>
+      <c r="N25" s="65"/>
+      <c r="O25" s="65"/>
+      <c r="P25" s="65"/>
+      <c r="Q25" s="65"/>
+      <c r="R25" s="65"/>
+      <c r="S25" s="65"/>
+      <c r="T25" s="65"/>
+      <c r="U25" s="65"/>
+      <c r="V25" s="65"/>
+      <c r="W25" s="65"/>
+      <c r="X25" s="65"/>
+      <c r="Y25" s="65"/>
+      <c r="Z25" s="73"/>
+      <c r="AA25" s="65"/>
+      <c r="AB25" s="65"/>
+      <c r="AC25" s="65"/>
+      <c r="AD25" s="65"/>
+      <c r="AE25" s="65"/>
+      <c r="AF25" s="65"/>
+      <c r="AG25" s="65"/>
+      <c r="AH25" s="65"/>
     </row>
     <row r="26" ht="14.25" customHeight="1">
-      <c r="A26" s="66"/>
-      <c r="B26" s="66"/>
-      <c r="C26" s="67"/>
-      <c r="D26" s="68"/>
-      <c r="E26" s="66"/>
-      <c r="F26" s="66"/>
-      <c r="G26" s="66"/>
-      <c r="H26" s="66"/>
-      <c r="I26" s="66"/>
-      <c r="J26" s="66"/>
-      <c r="K26" s="66"/>
-      <c r="L26" s="66"/>
-      <c r="M26" s="66"/>
-      <c r="N26" s="66"/>
-      <c r="O26" s="66"/>
-      <c r="P26" s="66"/>
-      <c r="Q26" s="66"/>
-      <c r="R26" s="66"/>
-      <c r="S26" s="66"/>
-      <c r="T26" s="66"/>
-      <c r="U26" s="66"/>
-      <c r="V26" s="66"/>
-      <c r="W26" s="66"/>
-      <c r="X26" s="66"/>
-      <c r="Y26" s="66"/>
-      <c r="Z26" s="74"/>
-      <c r="AA26" s="66"/>
-      <c r="AB26" s="66"/>
-      <c r="AC26" s="66"/>
-      <c r="AD26" s="66"/>
-      <c r="AE26" s="66"/>
-      <c r="AF26" s="66"/>
-      <c r="AG26" s="66"/>
-      <c r="AH26" s="66"/>
+      <c r="A26" s="65"/>
+      <c r="B26" s="65"/>
+      <c r="C26" s="66"/>
+      <c r="D26" s="67"/>
+      <c r="E26" s="65"/>
+      <c r="F26" s="65"/>
+      <c r="G26" s="65"/>
+      <c r="H26" s="65"/>
+      <c r="I26" s="65"/>
+      <c r="J26" s="65"/>
+      <c r="K26" s="65"/>
+      <c r="L26" s="65"/>
+      <c r="M26" s="65"/>
+      <c r="N26" s="65"/>
+      <c r="O26" s="65"/>
+      <c r="P26" s="65"/>
+      <c r="Q26" s="65"/>
+      <c r="R26" s="65"/>
+      <c r="S26" s="65"/>
+      <c r="T26" s="65"/>
+      <c r="U26" s="65"/>
+      <c r="V26" s="65"/>
+      <c r="W26" s="65"/>
+      <c r="X26" s="65"/>
+      <c r="Y26" s="65"/>
+      <c r="Z26" s="73"/>
+      <c r="AA26" s="65"/>
+      <c r="AB26" s="65"/>
+      <c r="AC26" s="65"/>
+      <c r="AD26" s="65"/>
+      <c r="AE26" s="65"/>
+      <c r="AF26" s="65"/>
+      <c r="AG26" s="65"/>
+      <c r="AH26" s="65"/>
     </row>
     <row r="27" ht="14.25" customHeight="1">
-      <c r="A27" s="66"/>
-      <c r="B27" s="66"/>
-      <c r="C27" s="67"/>
-      <c r="D27" s="68" t="s">
+      <c r="A27" s="65"/>
+      <c r="B27" s="65"/>
+      <c r="C27" s="66"/>
+      <c r="D27" s="67" t="s">
         <v>89</v>
       </c>
-      <c r="E27" s="66"/>
-      <c r="F27" s="66"/>
-      <c r="G27" s="66"/>
-      <c r="H27" s="66"/>
-      <c r="I27" s="66"/>
-      <c r="J27" s="66"/>
-      <c r="K27" s="66"/>
-      <c r="L27" s="68"/>
-      <c r="M27" s="68"/>
-      <c r="N27" s="66"/>
-      <c r="O27" s="68" t="s">
+      <c r="E27" s="65"/>
+      <c r="F27" s="65"/>
+      <c r="G27" s="65"/>
+      <c r="H27" s="65"/>
+      <c r="I27" s="65"/>
+      <c r="J27" s="65"/>
+      <c r="K27" s="65"/>
+      <c r="L27" s="67"/>
+      <c r="M27" s="67"/>
+      <c r="N27" s="65"/>
+      <c r="O27" s="67" t="s">
         <v>90</v>
       </c>
-      <c r="P27" s="68"/>
-      <c r="Q27" s="68"/>
-      <c r="R27" s="68"/>
-      <c r="S27" s="68" t="s">
+      <c r="P27" s="67"/>
+      <c r="Q27" s="67"/>
+      <c r="R27" s="67"/>
+      <c r="S27" s="67" t="s">
         <v>91</v>
       </c>
-      <c r="T27" s="68"/>
-      <c r="U27" s="68"/>
-      <c r="V27" s="68"/>
-      <c r="W27" s="68"/>
-      <c r="X27" s="68"/>
-      <c r="Y27" s="68" t="s">
+      <c r="T27" s="67"/>
+      <c r="U27" s="67"/>
+      <c r="V27" s="67"/>
+      <c r="W27" s="67"/>
+      <c r="X27" s="67"/>
+      <c r="Y27" s="67" t="s">
         <v>92</v>
       </c>
-      <c r="Z27" s="68"/>
-      <c r="AA27" s="66"/>
-      <c r="AB27" s="68"/>
-      <c r="AC27" s="68"/>
-      <c r="AD27" s="68"/>
-      <c r="AE27" s="66"/>
-      <c r="AF27" s="66"/>
-      <c r="AG27" s="66"/>
-      <c r="AH27" s="68"/>
+      <c r="Z27" s="67"/>
+      <c r="AA27" s="65"/>
+      <c r="AB27" s="67"/>
+      <c r="AC27" s="67"/>
+      <c r="AD27" s="67"/>
+      <c r="AE27" s="65"/>
+      <c r="AF27" s="65"/>
+      <c r="AG27" s="65"/>
+      <c r="AH27" s="67"/>
     </row>
     <row r="28" ht="14.25" customHeight="1">
-      <c r="A28" s="66"/>
-      <c r="B28" s="66"/>
-      <c r="C28" s="67"/>
-      <c r="D28" s="68" t="s">
+      <c r="A28" s="65"/>
+      <c r="B28" s="65"/>
+      <c r="C28" s="66"/>
+      <c r="D28" s="67" t="s">
         <v>93</v>
       </c>
-      <c r="E28" s="66"/>
-      <c r="F28" s="66"/>
-      <c r="G28" s="66"/>
-      <c r="H28" s="66"/>
-      <c r="I28" s="66"/>
-      <c r="J28" s="66"/>
-      <c r="K28" s="66"/>
-      <c r="L28" s="68"/>
-      <c r="M28" s="68"/>
-      <c r="N28" s="66"/>
-      <c r="O28" s="68" t="s">
+      <c r="E28" s="65"/>
+      <c r="F28" s="65"/>
+      <c r="G28" s="65"/>
+      <c r="H28" s="65"/>
+      <c r="I28" s="65"/>
+      <c r="J28" s="65"/>
+      <c r="K28" s="65"/>
+      <c r="L28" s="67"/>
+      <c r="M28" s="67"/>
+      <c r="N28" s="65"/>
+      <c r="O28" s="67" t="s">
         <v>94</v>
       </c>
-      <c r="P28" s="68"/>
-      <c r="Q28" s="68"/>
-      <c r="R28" s="68"/>
-      <c r="S28" s="68" t="s">
+      <c r="P28" s="67"/>
+      <c r="Q28" s="67"/>
+      <c r="R28" s="67"/>
+      <c r="S28" s="67" t="s">
         <v>95</v>
       </c>
-      <c r="T28" s="68"/>
-      <c r="U28" s="68"/>
-      <c r="V28" s="68"/>
-      <c r="W28" s="68"/>
-      <c r="X28" s="68"/>
-      <c r="Y28" s="68" t="s">
+      <c r="T28" s="67"/>
+      <c r="U28" s="67"/>
+      <c r="V28" s="67"/>
+      <c r="W28" s="67"/>
+      <c r="X28" s="67"/>
+      <c r="Y28" s="67" t="s">
         <v>96</v>
       </c>
-      <c r="Z28" s="69"/>
-      <c r="AA28" s="66"/>
-      <c r="AB28" s="68"/>
-      <c r="AC28" s="68"/>
-      <c r="AD28" s="68"/>
-      <c r="AE28" s="66"/>
-      <c r="AF28" s="66"/>
-      <c r="AG28" s="66"/>
-      <c r="AH28" s="68"/>
+      <c r="Z28" s="68"/>
+      <c r="AA28" s="65"/>
+      <c r="AB28" s="67"/>
+      <c r="AC28" s="67"/>
+      <c r="AD28" s="67"/>
+      <c r="AE28" s="65"/>
+      <c r="AF28" s="65"/>
+      <c r="AG28" s="65"/>
+      <c r="AH28" s="67"/>
     </row>
     <row r="29" ht="14.25" customHeight="1">
       <c r="A29" s="30"/>
